--- a/tables/N-Retention/Local_estpar_protection_False_vo_False_CUE_False.xlsx
+++ b/tables/N-Retention/Local_estpar_protection_False_vo_False_CUE_False.xlsx
@@ -573,61 +573,61 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5642466039963522</v>
+        <v>0.5642466029735214</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5600374693339812</v>
+        <v>0.5600374694374723</v>
       </c>
       <c r="M2" t="n">
-        <v>4.470333763738433</v>
+        <v>4.470333756123172</v>
       </c>
       <c r="N2" t="n">
-        <v>4.43899291592162</v>
+        <v>4.43899291669253</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001546624126309434</v>
+        <v>0.00154662386564543</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002814137399027153</v>
+        <v>0.002814137945910356</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001133089008509186</v>
+        <v>0.001133088933488361</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002112310674861011</v>
+        <v>0.002112310434973865</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001806132362842835</v>
+        <v>0.001806132305600312</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003259824167688535</v>
+        <v>0.003259820197074063</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005424675215112264</v>
+        <v>0.005424676804548841</v>
       </c>
       <c r="V2" t="n">
-        <v>0.002235909756949234</v>
+        <v>0.002235909601431854</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003562872541954754</v>
+        <v>0.003562871953083864</v>
       </c>
       <c r="X2" t="n">
-        <v>0.002227526340090697</v>
+        <v>0.00222752624234074</v>
       </c>
     </row>
     <row r="3">
@@ -653,61 +653,61 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5500633872661924</v>
+        <v>0.5500633869103069</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5569411876121438</v>
+        <v>0.556941187647178</v>
       </c>
       <c r="M3" t="n">
-        <v>4.364708589435769</v>
+        <v>4.364708586784724</v>
       </c>
       <c r="N3" t="n">
-        <v>4.415935012490094</v>
+        <v>4.415935012750933</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001588758894839178</v>
+        <v>0.001588758970723332</v>
       </c>
       <c r="P3" t="n">
         <v>1.000000000000001e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0009924300087750938</v>
+        <v>0.0009924300194388538</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001685493881098504</v>
+        <v>0.00168549393767081</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001059493480117187</v>
+        <v>0.001059493513998094</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007634601485445089</v>
+        <v>0.007634601547333728</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04305991836129051</v>
+        <v>0.04305991713848036</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002047021303717982</v>
+        <v>0.002047021387341907</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002446842706767911</v>
+        <v>0.002446842643632791</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001679867785416237</v>
+        <v>0.001679867767857725</v>
       </c>
     </row>
     <row r="4">
@@ -733,61 +733,61 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5593743245998097</v>
+        <v>0.5593743721000277</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5643120060630546</v>
+        <v>0.5643119952355042</v>
       </c>
       <c r="M4" t="n">
-        <v>4.434055121667282</v>
+        <v>4.434055475381553</v>
       </c>
       <c r="N4" t="n">
-        <v>4.470819430520934</v>
+        <v>4.470819349921603</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00258113314952185</v>
+        <v>0.002581127496786154</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001745499011047753</v>
+        <v>0.001745507419734734</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005278628316756731</v>
+        <v>0.0005278633745414758</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002273853386638826</v>
+        <v>0.002273852851567561</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001227588080283258</v>
+        <v>0.001227588253821656</v>
       </c>
       <c r="T4" t="n">
-        <v>0.006880098545868531</v>
+        <v>0.00688009389029583</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003522188553008305</v>
+        <v>0.003522217079409825</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001440601905576503</v>
+        <v>0.001440603005509302</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003986873003586963</v>
+        <v>0.003986871847035792</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002131972240501181</v>
+        <v>0.002131972943150874</v>
       </c>
     </row>
     <row r="5">
@@ -813,61 +813,61 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5455450639454225</v>
+        <v>0.5455450650049486</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5562164346600582</v>
+        <v>0.5562164350274201</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3310480335764</v>
+        <v>4.331048041470329</v>
       </c>
       <c r="N5" t="n">
-        <v>4.410535809851869</v>
+        <v>4.410535812588848</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00139478603674972</v>
+        <v>0.001394786356171256</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002420757369578511</v>
+        <v>0.002420755536310292</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001085171616750148</v>
+        <v>0.001085171677031365</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001869178572580884</v>
+        <v>0.001869178721123754</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002441127787479535</v>
+        <v>0.002441127919125292</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002952616741832286</v>
+        <v>0.00295262195564871</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00406635673195476</v>
+        <v>0.00406636715239898</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002209323478775711</v>
+        <v>0.002209323700330424</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002987851522812023</v>
+        <v>0.002987851671080803</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004248523124679143</v>
+        <v>0.004248522000736589</v>
       </c>
     </row>
     <row r="6">
@@ -893,61 +893,61 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5529797707778151</v>
+        <v>0.5529797710670845</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5586106926267251</v>
+        <v>0.5586106929415454</v>
       </c>
       <c r="M6" t="n">
-        <v>4.386431974980576</v>
+        <v>4.386431977135151</v>
       </c>
       <c r="N6" t="n">
-        <v>4.428367433275846</v>
+        <v>4.428367435620264</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001053331267576436</v>
+        <v>0.001053331316367589</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001804061670539093</v>
+        <v>0.00180406172197021</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0008112080990015909</v>
+        <v>0.0008112081044033951</v>
       </c>
       <c r="R6" t="n">
-        <v>0.000974842982857808</v>
+        <v>0.0009748430302527003</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00113780223125489</v>
+        <v>0.001137802268309332</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00214994142911684</v>
+        <v>0.002149941760105618</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002464389436393899</v>
+        <v>0.002464387858994156</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001639876459284904</v>
+        <v>0.001639876464298436</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001736764559291473</v>
+        <v>0.001736764618124773</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001623218662843244</v>
+        <v>0.001623218698544365</v>
       </c>
     </row>
     <row r="7">
@@ -973,61 +973,61 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5559179333411531</v>
+        <v>0.5559179311700849</v>
       </c>
       <c r="L7" t="n">
-        <v>0.555887341418285</v>
+        <v>0.5558873432468258</v>
       </c>
       <c r="M7" t="n">
-        <v>4.408315197949928</v>
+        <v>4.408315181780848</v>
       </c>
       <c r="N7" t="n">
-        <v>4.408087001257149</v>
+        <v>4.408087014877142</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001992078012741282</v>
+        <v>0.001992075918636438</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001764247282331164</v>
+        <v>0.001764247331978474</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008385461281850972</v>
+        <v>0.000838545716788506</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002598006332178813</v>
+        <v>0.002598003848186179</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001382605524367961</v>
+        <v>0.001382604659432207</v>
       </c>
       <c r="T7" t="n">
-        <v>0.004684343822198626</v>
+        <v>0.004684349008184043</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002835575757675359</v>
+        <v>0.002835552715396037</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001607628638983666</v>
+        <v>0.001607627801864437</v>
       </c>
       <c r="W7" t="n">
-        <v>0.004273559419943885</v>
+        <v>0.004273554541868022</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002560056537149477</v>
+        <v>0.002560056109927457</v>
       </c>
     </row>
     <row r="8">
@@ -1053,61 +1053,61 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5696724953710857</v>
+        <v>0.5696724962253498</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5581802004121954</v>
+        <v>0.5581802005868848</v>
       </c>
       <c r="M8" t="n">
-        <v>4.510727168591731</v>
+        <v>4.510727174950752</v>
       </c>
       <c r="N8" t="n">
-        <v>4.425159978479901</v>
+        <v>4.425159979780626</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002366180987267595</v>
+        <v>0.002366180766584308</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002300657301302344</v>
+        <v>0.002300657185618525</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001300664730677009</v>
+        <v>0.001300664687948085</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003175042568012543</v>
+        <v>0.003175042415376304</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002001043018253568</v>
+        <v>0.002001042976551999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.005520867012371213</v>
+        <v>0.005520867630290523</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004374253483646004</v>
+        <v>0.004374252491984888</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002697145935184929</v>
+        <v>0.002697145970265618</v>
       </c>
       <c r="W8" t="n">
-        <v>0.006224952648645582</v>
+        <v>0.006224954003703967</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00266802447554742</v>
+        <v>0.00266802337300972</v>
       </c>
     </row>
     <row r="9">
@@ -1133,61 +1133,61 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5453351465816443</v>
+        <v>0.5453351445704828</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5566118814591396</v>
+        <v>0.5566118819469267</v>
       </c>
       <c r="M9" t="n">
-        <v>4.329484052021317</v>
+        <v>4.329484037037172</v>
       </c>
       <c r="N9" t="n">
-        <v>4.413481034242892</v>
+        <v>4.413481037874798</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002291817782356676</v>
+        <v>0.002291818057415726</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002354175959316462</v>
+        <v>0.002354175876052922</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001091814223832011</v>
+        <v>0.001091814235237883</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002121312812368628</v>
+        <v>0.002121312848901857</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001710930353251549</v>
+        <v>0.00171093036882847</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005643569056426152</v>
+        <v>0.005643570269297345</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004181855759593553</v>
+        <v>0.004181856843437514</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002144973949532831</v>
+        <v>0.002144973972394866</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003475746234695619</v>
+        <v>0.003475745906084743</v>
       </c>
       <c r="X9" t="n">
-        <v>0.002591500255553078</v>
+        <v>0.002591500222552412</v>
       </c>
     </row>
     <row r="10">
@@ -1213,61 +1213,61 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5415086286978176</v>
+        <v>0.5415086242441041</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5458786736034196</v>
+        <v>0.5458786734502277</v>
       </c>
       <c r="M10" t="n">
-        <v>4.300972493242484</v>
+        <v>4.300972460055188</v>
       </c>
       <c r="N10" t="n">
-        <v>4.333533292292207</v>
+        <v>4.333533291151806</v>
       </c>
       <c r="O10" t="n">
-        <v>0.002053779766518537</v>
+        <v>0.002053778900840701</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002032010217240959</v>
+        <v>0.002032012656173436</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0008095652686133448</v>
+        <v>0.0008095652468369568</v>
       </c>
       <c r="R10" t="n">
-        <v>0.003728580007282999</v>
+        <v>0.003728579272440856</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001352188259529813</v>
+        <v>0.001352188728181657</v>
       </c>
       <c r="T10" t="n">
-        <v>0.00495911779964619</v>
+        <v>0.004959039116758534</v>
       </c>
       <c r="U10" t="n">
-        <v>0.003919063961821851</v>
+        <v>0.003919085236765904</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001559444610029203</v>
+        <v>0.001559444374304155</v>
       </c>
       <c r="W10" t="n">
-        <v>0.005580624698812091</v>
+        <v>0.005580598657136524</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001926584464235437</v>
+        <v>0.001926583401567152</v>
       </c>
     </row>
     <row r="11">
@@ -1293,61 +1293,61 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5232073771356348</v>
+        <v>0.5232073761328682</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5440093500033188</v>
+        <v>0.5440093507267233</v>
       </c>
       <c r="M11" t="n">
-        <v>4.164548646870926</v>
+        <v>4.164548639393129</v>
       </c>
       <c r="N11" t="n">
-        <v>4.319600221695777</v>
+        <v>4.319600227085206</v>
       </c>
       <c r="O11" t="n">
-        <v>0.002095023490404012</v>
+        <v>0.002095023783931476</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002229419797079219</v>
+        <v>0.002229419654308095</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001623633144571247</v>
+        <v>0.001623633275361836</v>
       </c>
       <c r="R11" t="n">
-        <v>0.004072726029630665</v>
+        <v>0.004072726182979367</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002933361272663391</v>
+        <v>0.00293336134322872</v>
       </c>
       <c r="T11" t="n">
-        <v>0.005397990445143372</v>
+        <v>0.00539798946157307</v>
       </c>
       <c r="U11" t="n">
-        <v>0.004715758787719159</v>
+        <v>0.004715758722951434</v>
       </c>
       <c r="V11" t="n">
-        <v>0.002993718286513183</v>
+        <v>0.002993718528511418</v>
       </c>
       <c r="W11" t="n">
-        <v>0.005292519012275193</v>
+        <v>0.00529252840753868</v>
       </c>
       <c r="X11" t="n">
-        <v>0.005120756626904633</v>
+        <v>0.005120756483917631</v>
       </c>
     </row>
     <row r="12">
@@ -1373,61 +1373,61 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4987727432373007</v>
+        <v>0.4987727401542309</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5387022031210887</v>
+        <v>0.538702201113907</v>
       </c>
       <c r="M12" t="n">
-        <v>3.982237472851482</v>
+        <v>3.982237449835301</v>
       </c>
       <c r="N12" t="n">
-        <v>4.280050129598065</v>
+        <v>4.280050114629518</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0006405095156440584</v>
+        <v>0.0006405087027060739</v>
       </c>
       <c r="P12" t="n">
-        <v>0.003658474172643294</v>
+        <v>0.0036584727289366</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0006497823263602997</v>
+        <v>0.0006497819224903523</v>
       </c>
       <c r="R12" t="n">
-        <v>0.007490643683975532</v>
+        <v>0.007490635390182233</v>
       </c>
       <c r="S12" t="n">
-        <v>0.001454176067370131</v>
+        <v>0.001454175335475599</v>
       </c>
       <c r="T12" t="n">
-        <v>0.00141650497146319</v>
+        <v>0.001416504516112534</v>
       </c>
       <c r="U12" t="n">
-        <v>0.004040312361447564</v>
+        <v>0.004040312135370344</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001308006213945124</v>
+        <v>0.00130800616253848</v>
       </c>
       <c r="W12" t="n">
-        <v>0.01077253346921594</v>
+        <v>0.01077250007456104</v>
       </c>
       <c r="X12" t="n">
-        <v>0.002191762010044083</v>
+        <v>0.002191763130757066</v>
       </c>
     </row>
     <row r="13">
@@ -1453,61 +1453,61 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5485841142950727</v>
+        <v>0.5485841172716791</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5654819848429546</v>
+        <v>0.5654819853281915</v>
       </c>
       <c r="M13" t="n">
-        <v>4.353688955519708</v>
+        <v>4.353688977694136</v>
       </c>
       <c r="N13" t="n">
-        <v>4.479527449743901</v>
+        <v>4.479527453357699</v>
       </c>
       <c r="O13" t="n">
-        <v>0.002730467309428572</v>
+        <v>0.002730467349932638</v>
       </c>
       <c r="P13" t="n">
-        <v>0.004092737744197404</v>
+        <v>0.004092737380614101</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001929402520674442</v>
+        <v>0.001929402512665817</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01349803292821742</v>
+        <v>0.01349803307435389</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01975314151465898</v>
+        <v>0.01975314102168717</v>
       </c>
       <c r="T13" t="n">
-        <v>0.009367239460012319</v>
+        <v>0.00936720837365791</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02314596897359799</v>
+        <v>0.02314567928955032</v>
       </c>
       <c r="V13" t="n">
-        <v>0.00709944629455841</v>
+        <v>0.007099446276538712</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02717119511673297</v>
+        <v>0.02717119628869247</v>
       </c>
       <c r="X13" t="n">
-        <v>0.04971931102892218</v>
+        <v>0.04971931366900689</v>
       </c>
     </row>
     <row r="14">
@@ -1533,61 +1533,61 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5536207568821496</v>
+        <v>0.5536207624284061</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5572253659036589</v>
+        <v>0.5572253669720449</v>
       </c>
       <c r="M14" t="n">
-        <v>4.391206196746249</v>
+        <v>4.391206238055635</v>
       </c>
       <c r="N14" t="n">
-        <v>4.418051427964776</v>
+        <v>4.418051435922582</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01144528236815232</v>
+        <v>0.01144527927297907</v>
       </c>
       <c r="P14" t="n">
-        <v>1.000000000006088e-05</v>
+        <v>1.000000000006171e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01225683428488068</v>
+        <v>0.01225683325692922</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01572566832934531</v>
+        <v>0.01572566700722078</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02596232586776919</v>
+        <v>0.02596232066382714</v>
       </c>
       <c r="T14" t="n">
-        <v>0.09451118278382636</v>
+        <v>0.09451117918663157</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3462061983705884</v>
+        <v>0.3462062318440825</v>
       </c>
       <c r="V14" t="n">
-        <v>0.02409742100172298</v>
+        <v>0.02409741848642014</v>
       </c>
       <c r="W14" t="n">
-        <v>0.02390450667699212</v>
+        <v>0.02390450604661322</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03961376993882517</v>
+        <v>0.03961376030082758</v>
       </c>
     </row>
     <row r="15">
@@ -1613,61 +1613,61 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.512220023929174</v>
+        <v>0.5122201226601502</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5474534594165504</v>
+        <v>0.5474534576590899</v>
       </c>
       <c r="M15" t="n">
-        <v>4.082594718855475</v>
+        <v>4.082595455460667</v>
       </c>
       <c r="N15" t="n">
-        <v>4.345250107716018</v>
+        <v>4.345250094677067</v>
       </c>
       <c r="O15" t="n">
-        <v>0.008241349885788772</v>
+        <v>0.008241346524905753</v>
       </c>
       <c r="P15" t="n">
-        <v>0.008118538682068134</v>
+        <v>0.008118547216853652</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.009736382457870268</v>
+        <v>0.009736379294842598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.01338696242749066</v>
+        <v>0.01338696192651662</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0504869551499989</v>
+        <v>0.0504868288838542</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01579241692557801</v>
+        <v>0.01579241260930328</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01373451768016657</v>
+        <v>0.01373457878022468</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01874564658102546</v>
+        <v>0.01874564016073132</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01869612145786727</v>
+        <v>0.01869612219401946</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2262077494784193</v>
+        <v>0.2262064682068308</v>
       </c>
     </row>
     <row r="16">
@@ -1693,61 +1693,61 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5547407510209781</v>
+        <v>0.5547407800811401</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5734821582779931</v>
+        <v>0.5734822454886035</v>
       </c>
       <c r="M16" t="n">
-        <v>4.399547914881411</v>
+        <v>4.399548131317051</v>
       </c>
       <c r="N16" t="n">
-        <v>4.539077565296358</v>
+        <v>4.53907821435329</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02796949386226819</v>
+        <v>0.02796949295173958</v>
       </c>
       <c r="P16" t="n">
-        <v>0.02003421251905571</v>
+        <v>0.02003421167117234</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.02180540941540461</v>
+        <v>0.02180540853047539</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01388633991859524</v>
+        <v>0.01388633935989157</v>
       </c>
       <c r="S16" t="n">
-        <v>0.006263433551753609</v>
+        <v>0.006263349591880999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2916227790431715</v>
+        <v>0.2916137994978541</v>
       </c>
       <c r="U16" t="n">
-        <v>0.262934803151423</v>
+        <v>0.2629257614800626</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2949069973461528</v>
+        <v>0.2948967926378642</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1716397859462628</v>
+        <v>0.1716339080856148</v>
       </c>
       <c r="X16" t="n">
-        <v>26.51235180071523</v>
+        <v>26.51115601394275</v>
       </c>
     </row>
     <row r="17">
@@ -1773,61 +1773,61 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5024881191354954</v>
+        <v>0.5024881234082471</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5289353004675135</v>
+        <v>0.5289352994939693</v>
       </c>
       <c r="M17" t="n">
-        <v>4.009971608901167</v>
+        <v>4.009971640793164</v>
       </c>
       <c r="N17" t="n">
-        <v>4.207233977756991</v>
+        <v>4.207233970505031</v>
       </c>
       <c r="O17" t="n">
-        <v>0.008705531429039317</v>
+        <v>0.008705532646870517</v>
       </c>
       <c r="P17" t="n">
-        <v>0.006213690784582681</v>
+        <v>0.006213689692481948</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.007777143273658206</v>
+        <v>0.00777714264619758</v>
       </c>
       <c r="R17" t="n">
-        <v>0.01210963357415608</v>
+        <v>0.01210963211385998</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0140100751659423</v>
+        <v>0.01401007223360037</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01740802795735213</v>
+        <v>0.01740820616000103</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0218929988874162</v>
+        <v>0.02189253984298209</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01452294994838491</v>
+        <v>0.01452295050568083</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0179667281080526</v>
+        <v>0.01796670673425712</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0262099132683823</v>
+        <v>0.0262099127666134</v>
       </c>
     </row>
     <row r="18">
@@ -1853,61 +1853,61 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5490011313733419</v>
+        <v>0.5490011262433148</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5506786814728655</v>
+        <v>0.5506786818181376</v>
       </c>
       <c r="M18" t="n">
-        <v>4.356795527549973</v>
+        <v>4.356795489334097</v>
       </c>
       <c r="N18" t="n">
-        <v>4.369291894828986</v>
+        <v>4.369291897400512</v>
       </c>
       <c r="O18" t="n">
-        <v>0.008834153098639847</v>
+        <v>0.008834154696658759</v>
       </c>
       <c r="P18" t="n">
-        <v>0.008750436495026286</v>
+        <v>0.008750427690661776</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.007770901067107725</v>
+        <v>0.007770901002742797</v>
       </c>
       <c r="R18" t="n">
-        <v>0.01806892995373932</v>
+        <v>0.0180689293637316</v>
       </c>
       <c r="S18" t="n">
-        <v>0.01616856070000633</v>
+        <v>0.01616856443489784</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01681492866582941</v>
+        <v>0.01681353579407954</v>
       </c>
       <c r="U18" t="n">
-        <v>0.01472462219161858</v>
+        <v>0.01472545334541623</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01414861325722953</v>
+        <v>0.01414858568260327</v>
       </c>
       <c r="W18" t="n">
-        <v>0.02673396228336938</v>
+        <v>0.02673386569381628</v>
       </c>
       <c r="X18" t="n">
-        <v>0.02352382729120811</v>
+        <v>0.02352370073145807</v>
       </c>
     </row>
     <row r="19">
@@ -1933,61 +1933,61 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4773251588100098</v>
+        <v>0.4773257066590098</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5579678973036085</v>
+        <v>0.5579678775240338</v>
       </c>
       <c r="M19" t="n">
-        <v>3.82203959903637</v>
+        <v>3.822043693296584</v>
       </c>
       <c r="N19" t="n">
-        <v>4.423535262046626</v>
+        <v>4.423535115113204</v>
       </c>
       <c r="O19" t="n">
-        <v>0.003377611604856392</v>
+        <v>0.003377610598732647</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0123452173533192</v>
+        <v>0.01234521478129885</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.00395806418222662</v>
+        <v>0.003958062740456406</v>
       </c>
       <c r="R19" t="n">
-        <v>0.003276483171618095</v>
+        <v>0.003276480380075385</v>
       </c>
       <c r="S19" t="n">
-        <v>0.07990371941465957</v>
+        <v>0.07990310488154155</v>
       </c>
       <c r="T19" t="n">
-        <v>0.009671750915201331</v>
+        <v>0.009671757332588933</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02573532788811163</v>
+        <v>0.02573538545466438</v>
       </c>
       <c r="V19" t="n">
-        <v>0.009842885573401282</v>
+        <v>0.009842885497682844</v>
       </c>
       <c r="W19" t="n">
-        <v>0.01091586669392167</v>
+        <v>0.01091587713495939</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6196216750545173</v>
+        <v>0.6192044498309046</v>
       </c>
     </row>
     <row r="20">
@@ -2013,61 +2013,61 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5783758603000023</v>
+        <v>0.5783758520538617</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5737768108250877</v>
+        <v>0.5737768050016634</v>
       </c>
       <c r="M20" t="n">
-        <v>4.575504098150747</v>
+        <v>4.575504036785888</v>
       </c>
       <c r="N20" t="n">
-        <v>4.541276363452692</v>
+        <v>4.541276320110899</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00646444386066719</v>
+        <v>0.006464444226888879</v>
       </c>
       <c r="P20" t="n">
-        <v>0.004689238372025442</v>
+        <v>0.004689241757423889</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.006779105304633425</v>
+        <v>0.006779105427592637</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009278118274229254</v>
+        <v>0.009278116940072632</v>
       </c>
       <c r="S20" t="n">
-        <v>0.04006958350345849</v>
+        <v>0.04006957724124588</v>
       </c>
       <c r="T20" t="n">
-        <v>0.01343864323294956</v>
+        <v>0.01343853481363024</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01968953757086848</v>
+        <v>0.01969022069456754</v>
       </c>
       <c r="V20" t="n">
-        <v>0.01294776588494626</v>
+        <v>0.01294776668609403</v>
       </c>
       <c r="W20" t="n">
-        <v>0.01787850317817046</v>
+        <v>0.01787850473966611</v>
       </c>
       <c r="X20" t="n">
-        <v>0.05975394343384821</v>
+        <v>0.05975400935312603</v>
       </c>
     </row>
     <row r="21">
@@ -2093,61 +2093,61 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5119505968393867</v>
+        <v>0.5119505969026676</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5213787263452643</v>
+        <v>0.5213787263607937</v>
       </c>
       <c r="M21" t="n">
-        <v>4.080584583903153</v>
+        <v>4.080584584375281</v>
       </c>
       <c r="N21" t="n">
-        <v>4.150903815996617</v>
+        <v>4.15090381611249</v>
       </c>
       <c r="O21" t="n">
-        <v>0.005639635455711436</v>
+        <v>0.005639635438614914</v>
       </c>
       <c r="P21" t="n">
-        <v>0.01978454819557003</v>
+        <v>0.01978454810503249</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.001936691368467081</v>
+        <v>0.001936691374547758</v>
       </c>
       <c r="R21" t="n">
-        <v>0.00314714169940986</v>
+        <v>0.003147141693485383</v>
       </c>
       <c r="S21" t="n">
-        <v>0.02137332562871849</v>
+        <v>0.0213733256318582</v>
       </c>
       <c r="T21" t="n">
-        <v>0.01198871036824219</v>
+        <v>0.01198870811426322</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0485109584786317</v>
+        <v>0.04851094207206648</v>
       </c>
       <c r="V21" t="n">
-        <v>0.007610641826160927</v>
+        <v>0.007610638755090889</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01544733776554973</v>
+        <v>0.01544733317408881</v>
       </c>
       <c r="X21" t="n">
-        <v>0.04307495191518745</v>
+        <v>0.04307497679517034</v>
       </c>
     </row>
     <row r="22">
@@ -2173,61 +2173,61 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5268307831677946</v>
+        <v>0.5268304488274074</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5503358981805936</v>
+        <v>0.5503357548184102</v>
       </c>
       <c r="M22" t="n">
-        <v>4.191566915241262</v>
+        <v>4.191564422390334</v>
       </c>
       <c r="N22" t="n">
-        <v>4.366725315194214</v>
+        <v>4.366724247030088</v>
       </c>
       <c r="O22" t="n">
-        <v>0.004558081514808567</v>
+        <v>0.004558036474337484</v>
       </c>
       <c r="P22" t="n">
-        <v>0.001838408016880636</v>
+        <v>0.001838380464197097</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.003342754512518366</v>
+        <v>0.003342724380837792</v>
       </c>
       <c r="R22" t="n">
-        <v>0.00581567743020506</v>
+        <v>0.005815615544478896</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01814365554641548</v>
+        <v>0.01814359950577899</v>
       </c>
       <c r="T22" t="n">
-        <v>0.01156837349668095</v>
+        <v>0.01156828638619914</v>
       </c>
       <c r="U22" t="n">
-        <v>0.01573237943617143</v>
+        <v>0.0157321056088608</v>
       </c>
       <c r="V22" t="n">
-        <v>0.009091871147111817</v>
+        <v>0.009091836970512331</v>
       </c>
       <c r="W22" t="n">
-        <v>0.01371023450130595</v>
+        <v>0.01371018421343835</v>
       </c>
       <c r="X22" t="n">
-        <v>0.04004801230798918</v>
+        <v>0.04004789699172601</v>
       </c>
     </row>
     <row r="23">
@@ -2253,61 +2253,61 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.484531289021057</v>
+        <v>0.4845312822572839</v>
       </c>
       <c r="L23" t="n">
-        <v>0.534404227697607</v>
+        <v>0.5344042282421178</v>
       </c>
       <c r="M23" t="n">
-        <v>3.875883377277486</v>
+        <v>3.875883326748309</v>
       </c>
       <c r="N23" t="n">
-        <v>4.247989258757823</v>
+        <v>4.247989262811854</v>
       </c>
       <c r="O23" t="n">
-        <v>0.00724482656660248</v>
+        <v>0.007244827119215701</v>
       </c>
       <c r="P23" t="n">
-        <v>0.006470964440814262</v>
+        <v>0.006470966709995011</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.005412924524552793</v>
+        <v>0.005412924870987578</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01779271472722548</v>
+        <v>0.01779271599922079</v>
       </c>
       <c r="S23" t="n">
-        <v>0.04574677405524962</v>
+        <v>0.04574678375012087</v>
       </c>
       <c r="T23" t="n">
-        <v>0.01532797569268178</v>
+        <v>0.01532799070159507</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0199263174814839</v>
+        <v>0.01992654689074496</v>
       </c>
       <c r="V23" t="n">
-        <v>0.01072547485907724</v>
+        <v>0.0107254751452588</v>
       </c>
       <c r="W23" t="n">
-        <v>0.02446829619589728</v>
+        <v>0.02446829553558132</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1967160289886419</v>
+        <v>0.1967161160143534</v>
       </c>
     </row>
     <row r="24">
@@ -2333,61 +2333,61 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5381273422429782</v>
+        <v>0.5381273409542512</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5470027408408563</v>
+        <v>0.547002739713621</v>
       </c>
       <c r="M24" t="n">
-        <v>4.275774819085798</v>
+        <v>4.275774809481438</v>
       </c>
       <c r="N24" t="n">
-        <v>4.34190649096697</v>
+        <v>4.341906482568857</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01203545559721172</v>
+        <v>0.01203545562202727</v>
       </c>
       <c r="P24" t="n">
-        <v>0.01004529823354628</v>
+        <v>0.01004529825579129</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.01499757294487271</v>
+        <v>0.01499757305856862</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01862265053993981</v>
+        <v>0.01862265047482825</v>
       </c>
       <c r="S24" t="n">
-        <v>0.00967468292000678</v>
+        <v>0.009674684907949491</v>
       </c>
       <c r="T24" t="n">
-        <v>0.03507891200501202</v>
+        <v>0.0350789073096866</v>
       </c>
       <c r="U24" t="n">
-        <v>0.05415999265245638</v>
+        <v>0.05415993384771214</v>
       </c>
       <c r="V24" t="n">
-        <v>0.05259305234620553</v>
+        <v>0.05259303522252935</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1261211523055847</v>
+        <v>0.1261210994671672</v>
       </c>
       <c r="X24" t="n">
-        <v>14.75414444609668</v>
+        <v>14.75414169250071</v>
       </c>
     </row>
     <row r="25">
@@ -2413,61 +2413,61 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5494012369207484</v>
+        <v>0.5494012367047949</v>
       </c>
       <c r="L25" t="n">
-        <v>0.553169863386759</v>
+        <v>0.5531698631861268</v>
       </c>
       <c r="M25" t="n">
-        <v>4.359776070804065</v>
+        <v>4.359776069195355</v>
       </c>
       <c r="N25" t="n">
-        <v>4.387847283084264</v>
+        <v>4.387847281589893</v>
       </c>
       <c r="O25" t="n">
-        <v>0.001157681547578076</v>
+        <v>0.001157681545332393</v>
       </c>
       <c r="P25" t="n">
-        <v>0.001157589154790366</v>
+        <v>0.001157589153162352</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0006302853211086022</v>
+        <v>0.000630285324941019</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0007832485721281111</v>
+        <v>0.000783248568483238</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0003838724546397517</v>
+        <v>0.0003838724562848627</v>
       </c>
       <c r="T25" t="n">
-        <v>0.002267958486245309</v>
+        <v>0.002267958484017728</v>
       </c>
       <c r="U25" t="n">
-        <v>0.00270899601992159</v>
+        <v>0.002708996019472673</v>
       </c>
       <c r="V25" t="n">
-        <v>0.00162140724802391</v>
+        <v>0.001621407251698243</v>
       </c>
       <c r="W25" t="n">
-        <v>0.002106701845915807</v>
+        <v>0.002106701842403449</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001540730271712957</v>
+        <v>0.00154073027034562</v>
       </c>
     </row>
     <row r="26">
@@ -2493,61 +2493,61 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.540731726273736</v>
+        <v>0.5407317262128234</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5490301157634917</v>
+        <v>0.5490301157157812</v>
       </c>
       <c r="M26" t="n">
-        <v>4.295183238249074</v>
+        <v>4.295183237795165</v>
       </c>
       <c r="N26" t="n">
-        <v>4.357008735272015</v>
+        <v>4.357008734916589</v>
       </c>
       <c r="O26" t="n">
-        <v>0.001938013741353031</v>
+        <v>0.001938013745720317</v>
       </c>
       <c r="P26" t="n">
-        <v>0.00221206757913711</v>
+        <v>0.002212067581264251</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0008933418646792555</v>
+        <v>0.0008933418625129237</v>
       </c>
       <c r="R26" t="n">
-        <v>0.00109962526127561</v>
+        <v>0.001099625263218435</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0006904394360973052</v>
+        <v>0.0006904394410452116</v>
       </c>
       <c r="T26" t="n">
-        <v>0.003211259008394061</v>
+        <v>0.00321125902224697</v>
       </c>
       <c r="U26" t="n">
-        <v>0.002694103808050452</v>
+        <v>0.002694103803596509</v>
       </c>
       <c r="V26" t="n">
-        <v>0.001847268570726132</v>
+        <v>0.001847268567995235</v>
       </c>
       <c r="W26" t="n">
-        <v>0.002219502083977518</v>
+        <v>0.002219502084793593</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001505072667080908</v>
+        <v>0.001505072665028954</v>
       </c>
     </row>
     <row r="27">
@@ -2573,61 +2573,61 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5300735358050577</v>
+        <v>0.5300735357526247</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5351353127961859</v>
+        <v>0.5351353127530093</v>
       </c>
       <c r="M27" t="n">
-        <v>4.215743336360242</v>
+        <v>4.215743335969353</v>
       </c>
       <c r="N27" t="n">
-        <v>4.253474005416254</v>
+        <v>4.253474005094433</v>
       </c>
       <c r="O27" t="n">
-        <v>0.001012555409788811</v>
+        <v>0.001012555408984809</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0014870157862833</v>
+        <v>0.001487015786357736</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.001305970100706782</v>
+        <v>0.001305970103206741</v>
       </c>
       <c r="R27" t="n">
-        <v>0.001362099750148501</v>
+        <v>0.001362099749066575</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0009913447928902482</v>
+        <v>0.0009913447929677784</v>
       </c>
       <c r="T27" t="n">
-        <v>0.00198880942730782</v>
+        <v>0.001988809427212056</v>
       </c>
       <c r="U27" t="n">
-        <v>0.002518024509117766</v>
+        <v>0.002518024506910382</v>
       </c>
       <c r="V27" t="n">
-        <v>0.002455191650071738</v>
+        <v>0.002455191654174869</v>
       </c>
       <c r="W27" t="n">
-        <v>0.002537847239220257</v>
+        <v>0.002537847237852919</v>
       </c>
       <c r="X27" t="n">
-        <v>0.002005688447121658</v>
+        <v>0.002005688447941687</v>
       </c>
     </row>
     <row r="28">
@@ -2653,61 +2653,61 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.5203824890675836</v>
+        <v>0.5203824972436116</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5470529690277872</v>
+        <v>0.5470529721959538</v>
       </c>
       <c r="M28" t="n">
-        <v>4.143481723210112</v>
+        <v>4.143481784187457</v>
       </c>
       <c r="N28" t="n">
-        <v>4.342274965088484</v>
+        <v>4.342274988687827</v>
       </c>
       <c r="O28" t="n">
-        <v>0.001450517945426016</v>
+        <v>0.001450515405969167</v>
       </c>
       <c r="P28" t="n">
-        <v>1.000000000000207e-05</v>
+        <v>1.000000000000848e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.001558353285690013</v>
+        <v>0.001558351815801817</v>
       </c>
       <c r="R28" t="n">
-        <v>0.006261812704481723</v>
+        <v>0.006261805468303037</v>
       </c>
       <c r="S28" t="n">
-        <v>0.01238708580136353</v>
+        <v>0.01238707096552571</v>
       </c>
       <c r="T28" t="n">
-        <v>0.003529540205740714</v>
+        <v>0.003529532197128905</v>
       </c>
       <c r="U28" t="n">
-        <v>0.009194181431709702</v>
+        <v>0.009194272459012791</v>
       </c>
       <c r="V28" t="n">
-        <v>0.00332599190585537</v>
+        <v>0.003325991956915125</v>
       </c>
       <c r="W28" t="n">
-        <v>0.01348139097100233</v>
+        <v>0.01348139057901449</v>
       </c>
       <c r="X28" t="n">
-        <v>0.03042858442612648</v>
+        <v>0.0304285845223375</v>
       </c>
     </row>
     <row r="29">
@@ -2733,61 +2733,61 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5450393411938402</v>
+        <v>0.5450393413035584</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5378439064658589</v>
+        <v>0.5378439064957135</v>
       </c>
       <c r="M29" t="n">
-        <v>4.327280143443206</v>
+        <v>4.327280144260669</v>
       </c>
       <c r="N29" t="n">
-        <v>4.273660911914124</v>
+        <v>4.273660912136644</v>
       </c>
       <c r="O29" t="n">
-        <v>0.003929893345178515</v>
+        <v>0.003929893332711217</v>
       </c>
       <c r="P29" t="n">
-        <v>0.01899259387671743</v>
+        <v>0.0189925936786421</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0009447870484310175</v>
+        <v>0.000944787063132475</v>
       </c>
       <c r="R29" t="n">
-        <v>0.02167819992120882</v>
+        <v>0.02167819989327526</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0105071624805524</v>
+        <v>0.01050716249094746</v>
       </c>
       <c r="T29" t="n">
-        <v>0.006426931862669509</v>
+        <v>0.006426931815995308</v>
       </c>
       <c r="U29" t="n">
-        <v>0.07519599170340231</v>
+        <v>0.07519598957619354</v>
       </c>
       <c r="V29" t="n">
-        <v>0.003536722927407943</v>
+        <v>0.003536722907099762</v>
       </c>
       <c r="W29" t="n">
-        <v>0.05000623514702596</v>
+        <v>0.05000623489004311</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01813806959402106</v>
+        <v>0.01813806960565919</v>
       </c>
     </row>
     <row r="30">
@@ -2813,61 +2813,61 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5803769440286095</v>
+        <v>0.5803769884098039</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5465348433022172</v>
+        <v>0.5465348378056645</v>
       </c>
       <c r="M30" t="n">
-        <v>4.590394956480194</v>
+        <v>4.590395286727254</v>
       </c>
       <c r="N30" t="n">
-        <v>4.338403044972283</v>
+        <v>4.338403003982189</v>
       </c>
       <c r="O30" t="n">
-        <v>0.002317713589538938</v>
+        <v>0.002317714998427606</v>
       </c>
       <c r="P30" t="n">
-        <v>0.005407526917715647</v>
+        <v>0.005407529641756727</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0006383842765301225</v>
+        <v>0.0006383852298351676</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01232556761745446</v>
+        <v>0.01232558388352168</v>
       </c>
       <c r="S30" t="n">
-        <v>0.005699870585962817</v>
+        <v>0.005699871831933943</v>
       </c>
       <c r="T30" t="n">
-        <v>0.004135164269589496</v>
+        <v>0.004135167112078122</v>
       </c>
       <c r="U30" t="n">
-        <v>0.009247870019645629</v>
+        <v>0.009247889609125729</v>
       </c>
       <c r="V30" t="n">
-        <v>0.00329606112391378</v>
+        <v>0.003296061292967356</v>
       </c>
       <c r="W30" t="n">
-        <v>0.0227679853710881</v>
+        <v>0.02276803047235075</v>
       </c>
       <c r="X30" t="n">
-        <v>0.007674195347436731</v>
+        <v>0.007674195351154705</v>
       </c>
     </row>
     <row r="31">
@@ -2893,61 +2893,61 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5411091241769229</v>
+        <v>0.5411091243856065</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5556978667155873</v>
+        <v>0.5556978668907762</v>
       </c>
       <c r="M31" t="n">
-        <v>4.297995521688784</v>
+        <v>4.297995523243836</v>
       </c>
       <c r="N31" t="n">
-        <v>4.406670651650804</v>
+        <v>4.406670652955556</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002482585655425598</v>
+        <v>0.002482585714528534</v>
       </c>
       <c r="P31" t="n">
-        <v>0.007465202381290556</v>
+        <v>0.00746520238740976</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0006461726625112033</v>
+        <v>0.0006461727029412601</v>
       </c>
       <c r="R31" t="n">
-        <v>0.002412704530710292</v>
+        <v>0.002412704574836931</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001226001704476962</v>
+        <v>0.001226001711208524</v>
       </c>
       <c r="T31" t="n">
-        <v>0.004252781974369944</v>
+        <v>0.004252782063407671</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01855833226933372</v>
+        <v>0.01855833198751329</v>
       </c>
       <c r="V31" t="n">
-        <v>0.002771415060403715</v>
+        <v>0.002771415086046717</v>
       </c>
       <c r="W31" t="n">
-        <v>0.003967572597895572</v>
+        <v>0.003967572620662782</v>
       </c>
       <c r="X31" t="n">
-        <v>0.003509555661825215</v>
+        <v>0.003509555647454621</v>
       </c>
     </row>
     <row r="32">
@@ -2973,61 +2973,61 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5785259936431176</v>
+        <v>0.5785259286975886</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5569642496622</v>
+        <v>0.5569642658630317</v>
       </c>
       <c r="M32" t="n">
-        <v>4.576621334530718</v>
+        <v>4.576620851231514</v>
       </c>
       <c r="N32" t="n">
-        <v>4.41609064602723</v>
+        <v>4.416090766784087</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0008324140239795527</v>
+        <v>0.000832412594005572</v>
       </c>
       <c r="P32" t="n">
-        <v>0.005225616144913479</v>
+        <v>0.005225607555272127</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.000000000033531e-05</v>
+        <v>1.000000000033804e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.00592955115043159</v>
+        <v>0.005929534895807368</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001961800586290341</v>
+        <v>0.001961798335946971</v>
       </c>
       <c r="T32" t="n">
-        <v>0.00242084692056028</v>
+        <v>0.002420845610897785</v>
       </c>
       <c r="U32" t="n">
-        <v>0.01137717000891556</v>
+        <v>0.0113771491744154</v>
       </c>
       <c r="V32" t="n">
-        <v>0.002535087797342961</v>
+        <v>0.002535088239485972</v>
       </c>
       <c r="W32" t="n">
-        <v>0.01157848904815869</v>
+        <v>0.01157844954904428</v>
       </c>
       <c r="X32" t="n">
-        <v>0.004406982058343866</v>
+        <v>0.004406980607236974</v>
       </c>
     </row>
     <row r="33">
@@ -3051,61 +3051,61 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5508868290868433</v>
+        <v>0.5508862626579282</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5457747739605538</v>
+        <v>0.5457747060608878</v>
       </c>
       <c r="M33" t="n">
-        <v>4.370842435405677</v>
+        <v>4.370838216122932</v>
       </c>
       <c r="N33" t="n">
-        <v>4.332759026763872</v>
+        <v>4.332758520978199</v>
       </c>
       <c r="O33" t="n">
-        <v>0.004966757549160781</v>
+        <v>0.004966856593430599</v>
       </c>
       <c r="P33" t="n">
-        <v>0.007359747586743497</v>
+        <v>0.007360169618402932</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003974386729172327</v>
+        <v>0.00397440477829034</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01612156677587081</v>
+        <v>0.01612154820180326</v>
       </c>
       <c r="S33" t="n">
-        <v>0.008266619212532231</v>
+        <v>0.008266610041037185</v>
       </c>
       <c r="T33" t="n">
-        <v>0.009902784371714294</v>
+        <v>0.009902931859880419</v>
       </c>
       <c r="U33" t="n">
-        <v>0.01680556142338027</v>
+        <v>0.01680652301804009</v>
       </c>
       <c r="V33" t="n">
-        <v>0.007231605074158981</v>
+        <v>0.007231615096541421</v>
       </c>
       <c r="W33" t="n">
-        <v>0.02544728915494122</v>
+        <v>0.02544707476556352</v>
       </c>
       <c r="X33" t="n">
-        <v>0.01237998608081989</v>
+        <v>0.01237987741486795</v>
       </c>
     </row>
     <row r="34">
@@ -3131,61 +3131,61 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.536901696262555</v>
+        <v>0.5369016959858964</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5432769441177873</v>
+        <v>0.5432769441207026</v>
       </c>
       <c r="M34" t="n">
-        <v>4.266640352725299</v>
+        <v>4.266640350663374</v>
       </c>
       <c r="N34" t="n">
-        <v>4.314148516785144</v>
+        <v>4.314148516806856</v>
       </c>
       <c r="O34" t="n">
-        <v>0.006370157979814552</v>
+        <v>0.006370157948108135</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01702657890431597</v>
+        <v>0.0170265795975241</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.003641605001491819</v>
+        <v>0.00364160498733877</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0178614884672569</v>
+        <v>0.01786148844866371</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0106640986111774</v>
+        <v>0.01066409856641214</v>
       </c>
       <c r="T34" t="n">
-        <v>0.01015912955820077</v>
+        <v>0.01015912948283414</v>
       </c>
       <c r="U34" t="n">
-        <v>0.08148469257749509</v>
+        <v>0.08148470136963391</v>
       </c>
       <c r="V34" t="n">
-        <v>0.004999184385137802</v>
+        <v>0.004999184378125962</v>
       </c>
       <c r="W34" t="n">
-        <v>0.02303028801158441</v>
+        <v>0.02303028803684702</v>
       </c>
       <c r="X34" t="n">
-        <v>0.009168973817179155</v>
+        <v>0.009168973752999167</v>
       </c>
     </row>
     <row r="35">
@@ -3211,61 +3211,61 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5002346248069625</v>
+        <v>0.5002346247082619</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5379442894222808</v>
+        <v>0.5379442894450083</v>
       </c>
       <c r="M35" t="n">
-        <v>3.9931505467131</v>
+        <v>3.993150545976317</v>
       </c>
       <c r="N35" t="n">
-        <v>4.27440784222261</v>
+        <v>4.274407842391886</v>
       </c>
       <c r="O35" t="n">
-        <v>0.001611441184099754</v>
+        <v>0.00161144110282491</v>
       </c>
       <c r="P35" t="n">
-        <v>0.4999999990094726</v>
+        <v>0.4999999989281275</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0009762445832650512</v>
+        <v>0.00097624456703288</v>
       </c>
       <c r="R35" t="n">
-        <v>0.01360902954286857</v>
+        <v>0.01360902921619599</v>
       </c>
       <c r="S35" t="n">
-        <v>0.002009111864874269</v>
+        <v>0.002009111828640706</v>
       </c>
       <c r="T35" t="n">
-        <v>0.003299999249372809</v>
+        <v>0.003299993121875727</v>
       </c>
       <c r="U35" t="n">
-        <v>1511.062226308233</v>
+        <v>1510.997414576618</v>
       </c>
       <c r="V35" t="n">
-        <v>0.002666321226439175</v>
+        <v>0.002666355930281581</v>
       </c>
       <c r="W35" t="n">
-        <v>0.02506078870613484</v>
+        <v>0.02505920097160078</v>
       </c>
       <c r="X35" t="n">
-        <v>0.003974751787812824</v>
+        <v>0.003975276176119884</v>
       </c>
     </row>
     <row r="36">
@@ -3291,61 +3291,61 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5508842687946176</v>
+        <v>0.5508842674969333</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5490937391614111</v>
+        <v>0.549093738428441</v>
       </c>
       <c r="M36" t="n">
-        <v>4.370823363997192</v>
+        <v>4.370823354330846</v>
       </c>
       <c r="N36" t="n">
-        <v>4.357485294707015</v>
+        <v>4.357485289246882</v>
       </c>
       <c r="O36" t="n">
-        <v>0.001148490572273193</v>
+        <v>0.001148490657381395</v>
       </c>
       <c r="P36" t="n">
-        <v>0.00307717957572216</v>
+        <v>0.003077179821902338</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0006854268294459944</v>
+        <v>0.0006854268940854434</v>
       </c>
       <c r="R36" t="n">
-        <v>0.002938435695939468</v>
+        <v>0.002938435850241455</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001999038289489383</v>
+        <v>0.001999038475037432</v>
       </c>
       <c r="T36" t="n">
-        <v>0.002811096147057301</v>
+        <v>0.002811096197717063</v>
       </c>
       <c r="U36" t="n">
-        <v>0.006337624750983241</v>
+        <v>0.006337625242553987</v>
       </c>
       <c r="V36" t="n">
-        <v>0.0028171002403565</v>
+        <v>0.002817100325132901</v>
       </c>
       <c r="W36" t="n">
-        <v>0.005461112347909127</v>
+        <v>0.005461112328953203</v>
       </c>
       <c r="X36" t="n">
-        <v>0.005692943070074919</v>
+        <v>0.005692942924321855</v>
       </c>
     </row>
     <row r="37">
@@ -3371,61 +3371,61 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5416254005209055</v>
+        <v>0.5416253932753577</v>
       </c>
       <c r="L37" t="n">
-        <v>0.5505769371026838</v>
+        <v>0.550576936651496</v>
       </c>
       <c r="M37" t="n">
-        <v>4.301842628273871</v>
+        <v>4.301842574283188</v>
       </c>
       <c r="N37" t="n">
-        <v>4.368532170683794</v>
+        <v>4.368532167320992</v>
       </c>
       <c r="O37" t="n">
-        <v>0.001951818300977434</v>
+        <v>0.001951818576311806</v>
       </c>
       <c r="P37" t="n">
-        <v>0.003775338346979587</v>
+        <v>0.003775338771766621</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.00139096401863458</v>
+        <v>0.001390964228688456</v>
       </c>
       <c r="R37" t="n">
-        <v>0.003290002677922407</v>
+        <v>0.00329000299451349</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0110011366368008</v>
+        <v>0.01100114189805684</v>
       </c>
       <c r="T37" t="n">
-        <v>0.004396327946248064</v>
+        <v>0.004396328350268141</v>
       </c>
       <c r="U37" t="n">
-        <v>0.005227424259818017</v>
+        <v>0.00522742439475259</v>
       </c>
       <c r="V37" t="n">
-        <v>0.003441097187980344</v>
+        <v>0.003441097567138962</v>
       </c>
       <c r="W37" t="n">
-        <v>0.005951835438401284</v>
+        <v>0.005951835504027688</v>
       </c>
       <c r="X37" t="n">
-        <v>0.02342911963956442</v>
+        <v>0.02342913954432578</v>
       </c>
     </row>
     <row r="38">
@@ -3451,61 +3451,61 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5410877791334675</v>
+        <v>0.5410877784062029</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5459458066566727</v>
+        <v>0.5459458049843995</v>
       </c>
       <c r="M38" t="n">
-        <v>4.297836464385832</v>
+        <v>4.297836458966457</v>
       </c>
       <c r="N38" t="n">
-        <v>4.334032058827635</v>
+        <v>4.334032046369179</v>
       </c>
       <c r="O38" t="n">
-        <v>0.002338921322743589</v>
+        <v>0.00233892084882577</v>
       </c>
       <c r="P38" t="n">
-        <v>0.001666349850650152</v>
+        <v>0.001666349601542721</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.001015483726897044</v>
+        <v>0.001015483449105355</v>
       </c>
       <c r="R38" t="n">
-        <v>0.002741039073618736</v>
+        <v>0.002741038489811496</v>
       </c>
       <c r="S38" t="n">
-        <v>0.007427259195261015</v>
+        <v>0.00742725776241806</v>
       </c>
       <c r="T38" t="n">
-        <v>0.005274645397900988</v>
+        <v>0.005274644632839331</v>
       </c>
       <c r="U38" t="n">
-        <v>0.002918253790409358</v>
+        <v>0.002918253733868105</v>
       </c>
       <c r="V38" t="n">
-        <v>0.002907041900607403</v>
+        <v>0.002907041609621463</v>
       </c>
       <c r="W38" t="n">
-        <v>0.00528189552377787</v>
+        <v>0.005281895229720768</v>
       </c>
       <c r="X38" t="n">
-        <v>0.01038654539914852</v>
+        <v>0.01038654664022216</v>
       </c>
     </row>
     <row r="39">
@@ -3531,61 +3531,61 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5532307663355256</v>
+        <v>0.5532307752309462</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5490907070150366</v>
+        <v>0.5490907096364179</v>
       </c>
       <c r="M39" t="n">
-        <v>4.388301465052076</v>
+        <v>4.388301531307524</v>
       </c>
       <c r="N39" t="n">
-        <v>4.357462340729385</v>
+        <v>4.357462360255743</v>
       </c>
       <c r="O39" t="n">
-        <v>0.002359992589827809</v>
+        <v>0.002359992861863835</v>
       </c>
       <c r="P39" t="n">
-        <v>0.003702430483569739</v>
+        <v>0.003702430575148988</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.001457906850969324</v>
+        <v>0.001457906954338344</v>
       </c>
       <c r="R39" t="n">
-        <v>0.00693351776837865</v>
+        <v>0.006933519811974364</v>
       </c>
       <c r="S39" t="n">
-        <v>0.003416305407835117</v>
+        <v>0.003416305715974498</v>
       </c>
       <c r="T39" t="n">
-        <v>0.004281865001445758</v>
+        <v>0.004281864773907172</v>
       </c>
       <c r="U39" t="n">
-        <v>0.005569409119699223</v>
+        <v>0.005569407861429469</v>
       </c>
       <c r="V39" t="n">
-        <v>0.003232027643082421</v>
+        <v>0.003232027481218742</v>
       </c>
       <c r="W39" t="n">
-        <v>0.009725194627759233</v>
+        <v>0.009725194048488013</v>
       </c>
       <c r="X39" t="n">
-        <v>0.004664106411195658</v>
+        <v>0.004664106324570991</v>
       </c>
     </row>
     <row r="40">
@@ -3611,61 +3611,61 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5283164027424528</v>
+        <v>0.528309914985073</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5696240457015206</v>
+        <v>0.5696241741013666</v>
       </c>
       <c r="M40" t="n">
-        <v>4.202643391765502</v>
+        <v>4.202595021857619</v>
       </c>
       <c r="N40" t="n">
-        <v>4.510363237697799</v>
+        <v>4.510364192862471</v>
       </c>
       <c r="O40" t="n">
-        <v>0.003943650533394083</v>
+        <v>0.003943786478417456</v>
       </c>
       <c r="P40" t="n">
-        <v>0.003411563931684859</v>
+        <v>0.003411550470100283</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.003249038607024133</v>
+        <v>0.00324906971573978</v>
       </c>
       <c r="R40" t="n">
-        <v>0.003625564940951341</v>
+        <v>0.003625631796828971</v>
       </c>
       <c r="S40" t="n">
-        <v>0.1307940840370163</v>
+        <v>0.1308154631128541</v>
       </c>
       <c r="T40" t="n">
-        <v>0.007324875141849316</v>
+        <v>0.007335035104021463</v>
       </c>
       <c r="U40" t="n">
-        <v>0.004370275899682704</v>
+        <v>0.00436840466247433</v>
       </c>
       <c r="V40" t="n">
-        <v>0.005371153513125084</v>
+        <v>0.005372099555761524</v>
       </c>
       <c r="W40" t="n">
-        <v>0.005726318705801799</v>
+        <v>0.005729825888889605</v>
       </c>
       <c r="X40" t="n">
-        <v>0.6190714950068744</v>
+        <v>0.6205338330392199</v>
       </c>
     </row>
     <row r="41">
@@ -3691,61 +3691,61 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5561311174839206</v>
+        <v>0.5561311111531306</v>
       </c>
       <c r="L41" t="n">
-        <v>0.5676406849696755</v>
+        <v>0.5676406721649624</v>
       </c>
       <c r="M41" t="n">
-        <v>4.409902885576174</v>
+        <v>4.409902838427838</v>
       </c>
       <c r="N41" t="n">
-        <v>4.495600230875197</v>
+        <v>4.495600135549877</v>
       </c>
       <c r="O41" t="n">
-        <v>0.001432619207972188</v>
+        <v>0.001432616358561027</v>
       </c>
       <c r="P41" t="n">
-        <v>0.004413349472934673</v>
+        <v>0.004413341988000165</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.001376381660799645</v>
+        <v>0.001376379370471382</v>
       </c>
       <c r="R41" t="n">
-        <v>0.001647575154645913</v>
+        <v>0.001647571569169665</v>
       </c>
       <c r="S41" t="n">
-        <v>0.007360167106256257</v>
+        <v>0.007360151143457548</v>
       </c>
       <c r="T41" t="n">
-        <v>0.002816501262550062</v>
+        <v>0.002816491619015612</v>
       </c>
       <c r="U41" t="n">
-        <v>0.006102750036912646</v>
+        <v>0.006102766753986552</v>
       </c>
       <c r="V41" t="n">
-        <v>0.002627392984833265</v>
+        <v>0.00262738988126989</v>
       </c>
       <c r="W41" t="n">
-        <v>0.003303018807386627</v>
+        <v>0.003303014070393121</v>
       </c>
       <c r="X41" t="n">
-        <v>0.01230065067803468</v>
+        <v>0.01230054371737495</v>
       </c>
     </row>
     <row r="42">
@@ -3771,61 +3771,61 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5695103219420882</v>
+        <v>0.5695090403804223</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5677355751121567</v>
+        <v>0.5677341791069864</v>
       </c>
       <c r="M42" t="n">
-        <v>4.509519969177892</v>
+        <v>4.509510429360552</v>
       </c>
       <c r="N42" t="n">
-        <v>4.496308434029389</v>
+        <v>4.496298041696225</v>
       </c>
       <c r="O42" t="n">
-        <v>0.004488067667775131</v>
+        <v>0.004488073698785614</v>
       </c>
       <c r="P42" t="n">
-        <v>0.005704053998342826</v>
+        <v>0.00570406339796363</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.004747924025282098</v>
+        <v>0.004747924055035635</v>
       </c>
       <c r="R42" t="n">
-        <v>0.004321378555986671</v>
+        <v>0.00432138439969914</v>
       </c>
       <c r="S42" t="n">
-        <v>0.004303061907079217</v>
+        <v>0.004304223039862032</v>
       </c>
       <c r="T42" t="n">
-        <v>0.07086136249602705</v>
+        <v>0.07104906901279633</v>
       </c>
       <c r="U42" t="n">
-        <v>0.1909550899203829</v>
+        <v>0.1909784518355396</v>
       </c>
       <c r="V42" t="n">
-        <v>0.05250014773204839</v>
+        <v>0.05260218168802564</v>
       </c>
       <c r="W42" t="n">
-        <v>0.09829641342649913</v>
+        <v>0.09846217741108573</v>
       </c>
       <c r="X42" t="n">
-        <v>33.30121045593854</v>
+        <v>33.36932215830577</v>
       </c>
     </row>
     <row r="43">
@@ -3851,61 +3851,61 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.4953620074672234</v>
+        <v>0.4953673905457935</v>
       </c>
       <c r="L43" t="n">
-        <v>0.5438608199689875</v>
+        <v>0.5438605780723469</v>
       </c>
       <c r="M43" t="n">
-        <v>3.956773080980899</v>
+        <v>3.956813274070416</v>
       </c>
       <c r="N43" t="n">
-        <v>4.318482601731036</v>
+        <v>4.318480801328295</v>
       </c>
       <c r="O43" t="n">
-        <v>0.0163698918005591</v>
+        <v>0.01636940356813838</v>
       </c>
       <c r="P43" t="n">
-        <v>0.01606019220577962</v>
+        <v>0.01606008551572558</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.01852461654579006</v>
+        <v>0.01852416706112711</v>
       </c>
       <c r="R43" t="n">
-        <v>0.04694255555013637</v>
+        <v>0.0469416971357321</v>
       </c>
       <c r="S43" t="n">
-        <v>0.09179738519732644</v>
+        <v>0.09178388587787553</v>
       </c>
       <c r="T43" t="n">
-        <v>0.02846644102360804</v>
+        <v>0.0284649921978222</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02301142855044225</v>
+        <v>0.02301132645397056</v>
       </c>
       <c r="V43" t="n">
-        <v>0.03469687274093801</v>
+        <v>0.03469576853122926</v>
       </c>
       <c r="W43" t="n">
-        <v>0.04773619621409929</v>
+        <v>0.04773510234734706</v>
       </c>
       <c r="X43" t="n">
-        <v>0.2547443716558618</v>
+        <v>0.2546772552725815</v>
       </c>
     </row>
     <row r="44">
@@ -3931,61 +3931,61 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5286870787682787</v>
+        <v>0.5286870788523486</v>
       </c>
       <c r="L44" t="n">
-        <v>0.5601500753340829</v>
+        <v>0.5601500753244641</v>
       </c>
       <c r="M44" t="n">
-        <v>4.205406969984286</v>
+        <v>4.205406970611064</v>
       </c>
       <c r="N44" t="n">
-        <v>4.439811321784974</v>
+        <v>4.439811321713447</v>
       </c>
       <c r="O44" t="n">
-        <v>0.03271704029141038</v>
+        <v>0.03271704027618151</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02441717894133158</v>
+        <v>0.02441717890143893</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.02212281777374925</v>
+        <v>0.0221228176652262</v>
       </c>
       <c r="R44" t="n">
-        <v>0.02308496603318283</v>
+        <v>0.02308496601756155</v>
       </c>
       <c r="S44" t="n">
-        <v>0.05343111858940566</v>
+        <v>0.05343111854570366</v>
       </c>
       <c r="T44" t="n">
-        <v>0.06370462302804071</v>
+        <v>0.06370462282802503</v>
       </c>
       <c r="U44" t="n">
-        <v>0.03180317974153177</v>
+        <v>0.03180317964852051</v>
       </c>
       <c r="V44" t="n">
-        <v>0.0430702891490072</v>
+        <v>0.04307028894329093</v>
       </c>
       <c r="W44" t="n">
-        <v>0.02966094837093374</v>
+        <v>0.02966094833997664</v>
       </c>
       <c r="X44" t="n">
-        <v>0.08761204451491394</v>
+        <v>0.08761204435006276</v>
       </c>
     </row>
     <row r="45">
@@ -4011,61 +4011,61 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5400703130547023</v>
+        <v>0.5400682057539532</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5561626704094714</v>
+        <v>0.5561630602657146</v>
       </c>
       <c r="M45" t="n">
-        <v>4.290254436529441</v>
+        <v>4.290238732877079</v>
       </c>
       <c r="N45" t="n">
-        <v>4.410136618536906</v>
+        <v>4.410139521744966</v>
       </c>
       <c r="O45" t="n">
-        <v>0.09555035461627759</v>
+        <v>0.09554874875990049</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1250915914571251</v>
+        <v>0.1250931591510586</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.07358513998912945</v>
+        <v>0.0735850187080641</v>
       </c>
       <c r="R45" t="n">
-        <v>0.1603984936262677</v>
+        <v>0.1603991817974873</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1985422221337302</v>
+        <v>0.1985671732430643</v>
       </c>
       <c r="T45" t="n">
-        <v>0.3285839385364094</v>
+        <v>0.3285720122474886</v>
       </c>
       <c r="U45" t="n">
-        <v>0.368312342267658</v>
+        <v>0.3683267143406719</v>
       </c>
       <c r="V45" t="n">
-        <v>0.1741461302697716</v>
+        <v>0.1741458253283941</v>
       </c>
       <c r="W45" t="n">
-        <v>0.4181644161022353</v>
+        <v>0.418170153888601</v>
       </c>
       <c r="X45" t="n">
-        <v>0.8008581742231349</v>
+        <v>0.8011280844810089</v>
       </c>
     </row>
     <row r="46">
@@ -4091,61 +4091,61 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4692195827002179</v>
+        <v>0.4692227989288898</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5639226084278881</v>
+        <v>0.5639225381280216</v>
       </c>
       <c r="M46" t="n">
-        <v>3.761450846446995</v>
+        <v>3.761474892830758</v>
       </c>
       <c r="N46" t="n">
-        <v>4.467884158084563</v>
+        <v>4.467883635561851</v>
       </c>
       <c r="O46" t="n">
-        <v>0.06328472078645837</v>
+        <v>0.06328466881218602</v>
       </c>
       <c r="P46" t="n">
-        <v>0.04462164018410317</v>
+        <v>0.04462163011382053</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.03204109986727702</v>
+        <v>0.03204109565159344</v>
       </c>
       <c r="R46" t="n">
-        <v>0.05109896705719571</v>
+        <v>0.0510989448345948</v>
       </c>
       <c r="S46" t="n">
-        <v>0.2440606428421472</v>
+        <v>0.2440482826360077</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1600066093206869</v>
+        <v>0.1600064158750759</v>
       </c>
       <c r="U46" t="n">
-        <v>0.08553689371680227</v>
+        <v>0.08553687401930028</v>
       </c>
       <c r="V46" t="n">
-        <v>0.04752251098581024</v>
+        <v>0.04752250777496061</v>
       </c>
       <c r="W46" t="n">
-        <v>0.07980915958113927</v>
+        <v>0.07980912133676514</v>
       </c>
       <c r="X46" t="n">
-        <v>2.891900819193784</v>
+        <v>2.891545098106384</v>
       </c>
     </row>
     <row r="47">
@@ -4171,61 +4171,61 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5376530400040005</v>
+        <v>0.5376530401280268</v>
       </c>
       <c r="L47" t="n">
-        <v>0.5539463945344929</v>
+        <v>0.5539463945369345</v>
       </c>
       <c r="M47" t="n">
-        <v>4.272240003116125</v>
+        <v>4.272240004040461</v>
       </c>
       <c r="N47" t="n">
-        <v>4.393626783533189</v>
+        <v>4.393626783551436</v>
       </c>
       <c r="O47" t="n">
-        <v>0.02629568054123893</v>
+        <v>0.02629568054744607</v>
       </c>
       <c r="P47" t="n">
-        <v>0.02041470948493697</v>
+        <v>0.02041470949021812</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.02389137395773333</v>
+        <v>0.02389137405215568</v>
       </c>
       <c r="R47" t="n">
-        <v>0.03290551379086816</v>
+        <v>0.03290551379655882</v>
       </c>
       <c r="S47" t="n">
-        <v>0.04923244189691206</v>
+        <v>0.0492324416134196</v>
       </c>
       <c r="T47" t="n">
-        <v>0.04780522201779444</v>
+        <v>0.04780522204310972</v>
       </c>
       <c r="U47" t="n">
-        <v>0.02798146392183112</v>
+        <v>0.02798146392272971</v>
       </c>
       <c r="V47" t="n">
-        <v>0.04733699667129609</v>
+        <v>0.04733699679048463</v>
       </c>
       <c r="W47" t="n">
-        <v>0.03885331549029692</v>
+        <v>0.038853315601297</v>
       </c>
       <c r="X47" t="n">
-        <v>0.06008300019995178</v>
+        <v>0.06008299907425721</v>
       </c>
     </row>
     <row r="48">
@@ -4251,61 +4251,61 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4047097120777118</v>
+        <v>0.4047095718033272</v>
       </c>
       <c r="L48" t="n">
-        <v>0.5472509420816788</v>
+        <v>0.5472509429512606</v>
       </c>
       <c r="M48" t="n">
-        <v>3.278188650913639</v>
+        <v>3.27818759776892</v>
       </c>
       <c r="N48" t="n">
-        <v>4.343715651178799</v>
+        <v>4.343715657605308</v>
       </c>
       <c r="O48" t="n">
-        <v>0.02657723951613876</v>
+        <v>0.0265772395201899</v>
       </c>
       <c r="P48" t="n">
-        <v>0.05274552791758433</v>
+        <v>0.05274552807042486</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.04243709189823286</v>
+        <v>0.04243709195863585</v>
       </c>
       <c r="R48" t="n">
-        <v>0.08900288061287753</v>
+        <v>0.08900288065764353</v>
       </c>
       <c r="S48" t="n">
-        <v>0.4372374145354189</v>
+        <v>0.4372380472155886</v>
       </c>
       <c r="T48" t="n">
-        <v>0.04810971543351892</v>
+        <v>0.04810971492986994</v>
       </c>
       <c r="U48" t="n">
-        <v>0.08841556091310868</v>
+        <v>0.08841556159837076</v>
       </c>
       <c r="V48" t="n">
-        <v>0.1013494155246297</v>
+        <v>0.101349414954587</v>
       </c>
       <c r="W48" t="n">
-        <v>0.09393475410431229</v>
+        <v>0.09393475367658047</v>
       </c>
       <c r="X48" t="n">
-        <v>10.59535791972128</v>
+        <v>10.59538949925502</v>
       </c>
     </row>
     <row r="49">
@@ -4331,61 +4331,61 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.5073340544510189</v>
+        <v>0.5073345342215706</v>
       </c>
       <c r="L49" t="n">
-        <v>0.5562862114575461</v>
+        <v>0.5562862247623941</v>
       </c>
       <c r="M49" t="n">
-        <v>4.046137816931932</v>
+        <v>4.046141397159318</v>
       </c>
       <c r="N49" t="n">
-        <v>4.411045032567057</v>
+        <v>4.411045131736945</v>
       </c>
       <c r="O49" t="n">
-        <v>0.01784116097772606</v>
+        <v>0.01784124470535089</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01400056420300008</v>
+        <v>0.01400056413842603</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.018016915935801</v>
+        <v>0.01801696139137551</v>
       </c>
       <c r="R49" t="n">
-        <v>0.02409727557868838</v>
+        <v>0.02409729139235045</v>
       </c>
       <c r="S49" t="n">
-        <v>0.1144102407284156</v>
+        <v>0.1144092452923137</v>
       </c>
       <c r="T49" t="n">
-        <v>0.03263539887753478</v>
+        <v>0.03263276649734481</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01747227595263373</v>
+        <v>0.01747362793110244</v>
       </c>
       <c r="V49" t="n">
-        <v>0.03253382044079071</v>
+        <v>0.03253374502549016</v>
       </c>
       <c r="W49" t="n">
-        <v>0.03561073952278947</v>
+        <v>0.0356100414072661</v>
       </c>
       <c r="X49" t="n">
-        <v>0.4095354221376856</v>
+        <v>0.409374524882662</v>
       </c>
     </row>
     <row r="50">
@@ -4411,61 +4411,61 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5409958952894117</v>
+        <v>0.540998905599272</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5609105796056079</v>
+        <v>0.5609127617027081</v>
       </c>
       <c r="M50" t="n">
-        <v>4.297151770118207</v>
+        <v>4.297174202195596</v>
       </c>
       <c r="N50" t="n">
-        <v>4.445470385809243</v>
+        <v>4.445486584110231</v>
       </c>
       <c r="O50" t="n">
-        <v>0.06486606026164178</v>
+        <v>0.06486632291762735</v>
       </c>
       <c r="P50" t="n">
-        <v>0.06452410122925463</v>
+        <v>0.06452418018592221</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.06516623177053395</v>
+        <v>0.06516618478440823</v>
       </c>
       <c r="R50" t="n">
-        <v>0.03600624296411507</v>
+        <v>0.03600617295366941</v>
       </c>
       <c r="S50" t="n">
-        <v>0.01136839625712979</v>
+        <v>0.01135174676225052</v>
       </c>
       <c r="T50" t="n">
-        <v>0.2270018663367448</v>
+        <v>0.2270669384296271</v>
       </c>
       <c r="U50" t="n">
-        <v>0.2636069185885194</v>
+        <v>0.2640638292175684</v>
       </c>
       <c r="V50" t="n">
-        <v>0.2679372505169348</v>
+        <v>0.268413893924108</v>
       </c>
       <c r="W50" t="n">
-        <v>0.1611465545386548</v>
+        <v>0.1615666609368926</v>
       </c>
       <c r="X50" t="n">
-        <v>14.3064493284135</v>
+        <v>14.32484121568235</v>
       </c>
     </row>
     <row r="51">
@@ -4491,61 +4491,61 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4812086802605804</v>
+        <v>0.4812090458799397</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5588663612374861</v>
+        <v>0.5588663725590283</v>
       </c>
       <c r="M51" t="n">
-        <v>3.851059526098112</v>
+        <v>3.851062257943341</v>
       </c>
       <c r="N51" t="n">
-        <v>4.430252432167871</v>
+        <v>4.430252516575232</v>
       </c>
       <c r="O51" t="n">
-        <v>0.05474557304944666</v>
+        <v>0.05474574679854656</v>
       </c>
       <c r="P51" t="n">
-        <v>0.04139987088441678</v>
+        <v>0.0413999229465196</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1289472612832484</v>
+        <v>0.1289473194543958</v>
       </c>
       <c r="R51" t="n">
-        <v>0.06407570240233228</v>
+        <v>0.06407579312780651</v>
       </c>
       <c r="S51" t="n">
-        <v>0.2179871846332974</v>
+        <v>0.217986333288868</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1326478479834944</v>
+        <v>0.1326488291261534</v>
       </c>
       <c r="U51" t="n">
-        <v>0.08255978716328416</v>
+        <v>0.08255991642362341</v>
       </c>
       <c r="V51" t="n">
-        <v>0.2293256315720723</v>
+        <v>0.229325703389019</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1199481010574502</v>
+        <v>0.1199482802202736</v>
       </c>
       <c r="X51" t="n">
-        <v>2.408586938743106</v>
+        <v>2.408617015401786</v>
       </c>
     </row>
     <row r="52">
@@ -4571,61 +4571,61 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5429836066241071</v>
+        <v>0.5429836102873031</v>
       </c>
       <c r="L52" t="n">
-        <v>0.5519919379474244</v>
+        <v>0.5519919380643462</v>
       </c>
       <c r="M52" t="n">
-        <v>4.311963123218198</v>
+        <v>4.3119631505133</v>
       </c>
       <c r="N52" t="n">
-        <v>4.379070425761204</v>
+        <v>4.379070426633709</v>
       </c>
       <c r="O52" t="n">
-        <v>0.01056980021685694</v>
+        <v>0.01056979969781632</v>
       </c>
       <c r="P52" t="n">
-        <v>0.01011734337544687</v>
+        <v>0.01011734309230839</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.01115439287387856</v>
+        <v>0.01115439212154074</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01267777671203137</v>
+        <v>0.01267777655208299</v>
       </c>
       <c r="S52" t="n">
-        <v>0.05214676690899978</v>
+        <v>0.05214674920908486</v>
       </c>
       <c r="T52" t="n">
-        <v>0.01781992051110715</v>
+        <v>0.01781991963489088</v>
       </c>
       <c r="U52" t="n">
-        <v>0.01393050101495484</v>
+        <v>0.01393050081159345</v>
       </c>
       <c r="V52" t="n">
-        <v>0.02010213452782804</v>
+        <v>0.02010213291821791</v>
       </c>
       <c r="W52" t="n">
-        <v>0.01949607486565501</v>
+        <v>0.01949607489855787</v>
       </c>
       <c r="X52" t="n">
-        <v>0.08528346792340756</v>
+        <v>0.08528342039959375</v>
       </c>
     </row>
     <row r="53">
@@ -4651,61 +4651,61 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5670780971791589</v>
+        <v>0.5670778507893233</v>
       </c>
       <c r="L53" t="n">
-        <v>0.5590985074309123</v>
+        <v>0.5590985451521717</v>
       </c>
       <c r="M53" t="n">
-        <v>4.491413962140649</v>
+        <v>4.491412127883297</v>
       </c>
       <c r="N53" t="n">
-        <v>4.432000645325143</v>
+        <v>4.432000926257783</v>
       </c>
       <c r="O53" t="n">
-        <v>0.02319119139612391</v>
+        <v>0.02319090298872542</v>
       </c>
       <c r="P53" t="n">
-        <v>0.02139431979860311</v>
+        <v>0.02139424542685245</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.01465897599943995</v>
+        <v>0.01465888371442974</v>
       </c>
       <c r="R53" t="n">
-        <v>0.04043111999659581</v>
+        <v>0.04043057739340169</v>
       </c>
       <c r="S53" t="n">
-        <v>0.1947718166515042</v>
+        <v>0.1947715854347059</v>
       </c>
       <c r="T53" t="n">
-        <v>0.0417631666891083</v>
+        <v>0.04176280465430789</v>
       </c>
       <c r="U53" t="n">
-        <v>0.02785090451099996</v>
+        <v>0.02785056231072388</v>
       </c>
       <c r="V53" t="n">
-        <v>0.02326946835578939</v>
+        <v>0.02326931605344258</v>
       </c>
       <c r="W53" t="n">
-        <v>0.06394281369907574</v>
+        <v>0.06394240029502722</v>
       </c>
       <c r="X53" t="n">
-        <v>0.2253048187616115</v>
+        <v>0.2253175585103827</v>
       </c>
     </row>
     <row r="54">
@@ -4731,61 +4731,61 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5192367329134363</v>
+        <v>0.5192366779258668</v>
       </c>
       <c r="L54" t="n">
-        <v>0.5516936481741016</v>
+        <v>0.5516936300760367</v>
       </c>
       <c r="M54" t="n">
-        <v>4.134936389104962</v>
+        <v>4.13493597898387</v>
       </c>
       <c r="N54" t="n">
-        <v>4.376824580745172</v>
+        <v>4.376824445931637</v>
       </c>
       <c r="O54" t="n">
-        <v>0.02366982034889333</v>
+        <v>0.02366978531752076</v>
       </c>
       <c r="P54" t="n">
-        <v>0.01134844691366935</v>
+        <v>0.01134843649833913</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.02116630480871329</v>
+        <v>0.02116622118699732</v>
       </c>
       <c r="R54" t="n">
-        <v>0.01626396333751453</v>
+        <v>0.01626395802642771</v>
       </c>
       <c r="S54" t="n">
-        <v>0.03788836830077404</v>
+        <v>0.0378884190973334</v>
       </c>
       <c r="T54" t="n">
-        <v>0.0463535583204047</v>
+        <v>0.04635349333321947</v>
       </c>
       <c r="U54" t="n">
-        <v>0.01692067265034248</v>
+        <v>0.01692068544815939</v>
       </c>
       <c r="V54" t="n">
-        <v>0.04257634312703989</v>
+        <v>0.04257613660173279</v>
       </c>
       <c r="W54" t="n">
-        <v>0.02038569318035237</v>
+        <v>0.02038569629379097</v>
       </c>
       <c r="X54" t="n">
-        <v>0.06186150928793351</v>
+        <v>0.06186164551178028</v>
       </c>
     </row>
     <row r="55">
@@ -4811,61 +4811,61 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5563410684470536</v>
+        <v>0.5563410613774147</v>
       </c>
       <c r="L55" t="n">
-        <v>0.5566584362643872</v>
+        <v>0.5566584338045375</v>
       </c>
       <c r="M55" t="n">
-        <v>4.411466481943051</v>
+        <v>4.411466429292571</v>
       </c>
       <c r="N55" t="n">
-        <v>4.413829990274611</v>
+        <v>4.413829971954925</v>
       </c>
       <c r="O55" t="n">
-        <v>0.01441577564158451</v>
+        <v>0.01441577584812513</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01152247750821992</v>
+        <v>0.01152247618741628</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.0140921803529396</v>
+        <v>0.01409213965648441</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01937289732091652</v>
+        <v>0.01937289029503</v>
       </c>
       <c r="S55" t="n">
-        <v>0.02369517456785546</v>
+        <v>0.02369516407625974</v>
       </c>
       <c r="T55" t="n">
-        <v>0.02403412601901622</v>
+        <v>0.02403419100325719</v>
       </c>
       <c r="U55" t="n">
-        <v>0.01606521329911698</v>
+        <v>0.01606522092795421</v>
       </c>
       <c r="V55" t="n">
-        <v>0.02562914103053825</v>
+        <v>0.02562904057471246</v>
       </c>
       <c r="W55" t="n">
-        <v>0.02303134498141871</v>
+        <v>0.02303134658393208</v>
       </c>
       <c r="X55" t="n">
-        <v>0.02558251390753268</v>
+        <v>0.02558255428116063</v>
       </c>
     </row>
     <row r="56">
@@ -4891,61 +4891,61 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5097180810386136</v>
+        <v>0.5097180812285835</v>
       </c>
       <c r="L56" t="n">
-        <v>0.5521349186700187</v>
+        <v>0.5521349186664659</v>
       </c>
       <c r="M56" t="n">
-        <v>4.063927352245716</v>
+        <v>4.063927353663189</v>
       </c>
       <c r="N56" t="n">
-        <v>4.380121791248679</v>
+        <v>4.380121791222325</v>
       </c>
       <c r="O56" t="n">
-        <v>0.01788283889818332</v>
+        <v>0.01788283889402423</v>
       </c>
       <c r="P56" t="n">
-        <v>0.01340615818860914</v>
+        <v>0.01340615820661926</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.01476816841035354</v>
+        <v>0.01476816845092419</v>
       </c>
       <c r="R56" t="n">
-        <v>0.02550269428741145</v>
+        <v>0.0255026943091674</v>
       </c>
       <c r="S56" t="n">
-        <v>0.05919001245145147</v>
+        <v>0.05919001225645634</v>
       </c>
       <c r="T56" t="n">
-        <v>0.03154746106001149</v>
+        <v>0.03154746099517089</v>
       </c>
       <c r="U56" t="n">
-        <v>0.01852511120146979</v>
+        <v>0.0185251112666143</v>
       </c>
       <c r="V56" t="n">
-        <v>0.02751403081654895</v>
+        <v>0.02751403087410189</v>
       </c>
       <c r="W56" t="n">
-        <v>0.03508856474236026</v>
+        <v>0.03508856479366628</v>
       </c>
       <c r="X56" t="n">
-        <v>0.1402670044442715</v>
+        <v>0.1402670047527875</v>
       </c>
     </row>
     <row r="57">
@@ -4971,61 +4971,61 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5362984060044483</v>
+        <v>0.5362984060841561</v>
       </c>
       <c r="L57" t="n">
-        <v>0.5545372151083801</v>
+        <v>0.5545372150903707</v>
       </c>
       <c r="M57" t="n">
-        <v>4.26214400069415</v>
+        <v>4.262144001288224</v>
       </c>
       <c r="N57" t="n">
-        <v>4.398024514826248</v>
+        <v>4.398024514692201</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02335415796389578</v>
+        <v>0.02335415789816163</v>
       </c>
       <c r="P57" t="n">
-        <v>0.01055041984585022</v>
+        <v>0.01055041984106579</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01749190118172447</v>
+        <v>0.01749190112285755</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01872592063907398</v>
+        <v>0.01872592065414534</v>
       </c>
       <c r="S57" t="n">
-        <v>0.02947005120761005</v>
+        <v>0.0294700511204646</v>
       </c>
       <c r="T57" t="n">
-        <v>0.0443214406298665</v>
+        <v>0.04432144036737171</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01564946283566307</v>
+        <v>0.01564946282173266</v>
       </c>
       <c r="V57" t="n">
-        <v>0.03067597931135057</v>
+        <v>0.03067597917244633</v>
       </c>
       <c r="W57" t="n">
-        <v>0.02492786669493469</v>
+        <v>0.02492786675848525</v>
       </c>
       <c r="X57" t="n">
-        <v>0.04086461391742603</v>
+        <v>0.04086461377210767</v>
       </c>
     </row>
     <row r="58">
@@ -5051,61 +5051,61 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5115706784830822</v>
+        <v>0.5115706920577616</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5661461273494589</v>
+        <v>0.5661461673117506</v>
       </c>
       <c r="M58" t="n">
-        <v>4.077750057352576</v>
+        <v>4.077750158632536</v>
       </c>
       <c r="N58" t="n">
-        <v>4.484399774125411</v>
+        <v>4.484400071656055</v>
       </c>
       <c r="O58" t="n">
-        <v>0.05365326253743708</v>
+        <v>0.05365341711143792</v>
       </c>
       <c r="P58" t="n">
-        <v>0.01193525770029569</v>
+        <v>0.01193528715249321</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.04519841405302951</v>
+        <v>0.04519849262531122</v>
       </c>
       <c r="R58" t="n">
-        <v>0.01328469298960752</v>
+        <v>0.01328471382988618</v>
       </c>
       <c r="S58" t="n">
-        <v>0.06845898998183562</v>
+        <v>0.06845902807778234</v>
       </c>
       <c r="T58" t="n">
-        <v>0.1268384249995336</v>
+        <v>0.1268285392943137</v>
       </c>
       <c r="U58" t="n">
-        <v>0.01892564226061464</v>
+        <v>0.0189240677582284</v>
       </c>
       <c r="V58" t="n">
-        <v>0.1083872798531441</v>
+        <v>0.1083900948376585</v>
       </c>
       <c r="W58" t="n">
-        <v>0.01907249308574491</v>
+        <v>0.01907211884924622</v>
       </c>
       <c r="X58" t="n">
-        <v>0.1320147091548337</v>
+        <v>0.1320164063748199</v>
       </c>
     </row>
     <row r="59">
@@ -5131,61 +5131,61 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5293059348727757</v>
+        <v>0.529305935645196</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5538338158486154</v>
+        <v>0.5538338154450453</v>
       </c>
       <c r="M59" t="n">
-        <v>4.210020762317669</v>
+        <v>4.210020768076263</v>
       </c>
       <c r="N59" t="n">
-        <v>4.392782555440949</v>
+        <v>4.392782552435599</v>
       </c>
       <c r="O59" t="n">
-        <v>0.01029833608232163</v>
+        <v>0.01029833533417803</v>
       </c>
       <c r="P59" t="n">
-        <v>0.004539144323541964</v>
+        <v>0.00453914424498581</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.008650096836568687</v>
+        <v>0.008650096759533005</v>
       </c>
       <c r="R59" t="n">
-        <v>0.007098065092985744</v>
+        <v>0.007098064930533415</v>
       </c>
       <c r="S59" t="n">
-        <v>0.00822416294863002</v>
+        <v>0.008224162736488839</v>
       </c>
       <c r="T59" t="n">
-        <v>0.01676074210330156</v>
+        <v>0.01676074233610583</v>
       </c>
       <c r="U59" t="n">
-        <v>0.005541944152225409</v>
+        <v>0.005541944080237548</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01143190424185291</v>
+        <v>0.01143190326471464</v>
       </c>
       <c r="W59" t="n">
-        <v>0.006676033978372371</v>
+        <v>0.00667603427183447</v>
       </c>
       <c r="X59" t="n">
-        <v>0.007331851313612147</v>
+        <v>0.007331851557140006</v>
       </c>
     </row>
     <row r="60">
@@ -5211,61 +5211,61 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.520091897588902</v>
+        <v>0.5200918946229371</v>
       </c>
       <c r="L60" t="n">
-        <v>0.5420607107055893</v>
+        <v>0.5420607064299383</v>
       </c>
       <c r="M60" t="n">
-        <v>4.141314459674549</v>
+        <v>4.141314437553916</v>
       </c>
       <c r="N60" t="n">
-        <v>4.30507491140169</v>
+        <v>4.305074879542543</v>
       </c>
       <c r="O60" t="n">
-        <v>0.002688510826234986</v>
+        <v>0.002688509876704253</v>
       </c>
       <c r="P60" t="n">
-        <v>0.004443635269329842</v>
+        <v>0.004443631870204095</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.001399026473855564</v>
+        <v>0.001399025702763169</v>
       </c>
       <c r="R60" t="n">
-        <v>0.004570396915047842</v>
+        <v>0.004570395180094162</v>
       </c>
       <c r="S60" t="n">
-        <v>0.00879421067319191</v>
+        <v>0.008794208760202702</v>
       </c>
       <c r="T60" t="n">
-        <v>0.003856969144677906</v>
+        <v>0.003856968448603529</v>
       </c>
       <c r="U60" t="n">
-        <v>0.005279303190128591</v>
+        <v>0.005279299429339826</v>
       </c>
       <c r="V60" t="n">
-        <v>0.002241673457764175</v>
+        <v>0.002241672900072007</v>
       </c>
       <c r="W60" t="n">
-        <v>0.005061016126528004</v>
+        <v>0.005061013846246434</v>
       </c>
       <c r="X60" t="n">
-        <v>0.009739714992418713</v>
+        <v>0.009739738059253156</v>
       </c>
     </row>
     <row r="61">
@@ -5291,61 +5291,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4963841461331371</v>
+        <v>0.4963830729515357</v>
       </c>
       <c r="L61" t="n">
-        <v>0.5421099984947653</v>
+        <v>0.542110098961874</v>
       </c>
       <c r="M61" t="n">
-        <v>3.964404756002983</v>
+        <v>3.964396743418508</v>
       </c>
       <c r="N61" t="n">
-        <v>4.305440748236789</v>
+        <v>4.305441496515058</v>
       </c>
       <c r="O61" t="n">
-        <v>0.005813544327908549</v>
+        <v>0.005813616464947611</v>
       </c>
       <c r="P61" t="n">
-        <v>0.009128243468635463</v>
+        <v>0.009128353720522729</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.003442883375330522</v>
+        <v>0.003442905644568553</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01951583818648579</v>
+        <v>0.01951594472676581</v>
       </c>
       <c r="S61" t="n">
-        <v>0.03953710599237037</v>
+        <v>0.03953846386829551</v>
       </c>
       <c r="T61" t="n">
-        <v>0.007890773444999671</v>
+        <v>0.007890860946888893</v>
       </c>
       <c r="U61" t="n">
-        <v>0.009685956932164353</v>
+        <v>0.009686037381253168</v>
       </c>
       <c r="V61" t="n">
-        <v>0.004259575712599083</v>
+        <v>0.004259596036048635</v>
       </c>
       <c r="W61" t="n">
-        <v>0.01795909778452318</v>
+        <v>0.01795911994091073</v>
       </c>
       <c r="X61" t="n">
-        <v>0.1574033310244314</v>
+        <v>0.1574141801079077</v>
       </c>
     </row>
     <row r="62">
@@ -5371,61 +5371,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.5450073111588626</v>
+        <v>0.5450073111550779</v>
       </c>
       <c r="L62" t="n">
-        <v>0.5421374368154698</v>
+        <v>0.5421374368546221</v>
       </c>
       <c r="M62" t="n">
-        <v>4.327041501018048</v>
+        <v>4.32704150098985</v>
       </c>
       <c r="N62" t="n">
-        <v>4.30565773335548</v>
+        <v>4.305657733647206</v>
       </c>
       <c r="O62" t="n">
-        <v>0.008443613589818801</v>
+        <v>0.008443613695666945</v>
       </c>
       <c r="P62" t="n">
-        <v>0.00408597347285107</v>
+        <v>0.004085973419140442</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.004573381924675803</v>
+        <v>0.004573381931169999</v>
       </c>
       <c r="R62" t="n">
-        <v>0.0333823111515428</v>
+        <v>0.03338231158045723</v>
       </c>
       <c r="S62" t="n">
-        <v>0.01741399863966991</v>
+        <v>0.0174139988796689</v>
       </c>
       <c r="T62" t="n">
-        <v>0.01376137712089624</v>
+        <v>0.01376138070736773</v>
       </c>
       <c r="U62" t="n">
-        <v>0.008240245210930537</v>
+        <v>0.008240287709562328</v>
       </c>
       <c r="V62" t="n">
-        <v>0.005654544794451238</v>
+        <v>0.005654544744851726</v>
       </c>
       <c r="W62" t="n">
-        <v>0.05190564106228814</v>
+        <v>0.05190563901637764</v>
       </c>
       <c r="X62" t="n">
-        <v>0.03268376726399522</v>
+        <v>0.03268376794354033</v>
       </c>
     </row>
     <row r="63">
@@ -5451,61 +5451,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.5050331926392827</v>
+        <v>0.5050340113780182</v>
       </c>
       <c r="L63" t="n">
-        <v>0.542244670135654</v>
+        <v>0.5422447535631931</v>
       </c>
       <c r="M63" t="n">
-        <v>4.028967021104512</v>
+        <v>4.028973131483649</v>
       </c>
       <c r="N63" t="n">
-        <v>4.306444032513134</v>
+        <v>4.306444654447003</v>
       </c>
       <c r="O63" t="n">
-        <v>0.006180118639045546</v>
+        <v>0.006180249578634286</v>
       </c>
       <c r="P63" t="n">
-        <v>0.006787722892565009</v>
+        <v>0.00678736896980619</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.003238529003066795</v>
+        <v>0.003238537775078277</v>
       </c>
       <c r="R63" t="n">
-        <v>0.01677426118745507</v>
+        <v>0.01677437133651295</v>
       </c>
       <c r="S63" t="n">
-        <v>0.02621714135876263</v>
+        <v>0.02621649273868816</v>
       </c>
       <c r="T63" t="n">
-        <v>0.009111240958338929</v>
+        <v>0.009111581878401451</v>
       </c>
       <c r="U63" t="n">
-        <v>0.008938628213199531</v>
+        <v>0.008938642127981376</v>
       </c>
       <c r="V63" t="n">
-        <v>0.003848731337181309</v>
+        <v>0.003848737385668645</v>
       </c>
       <c r="W63" t="n">
-        <v>0.01691348104961822</v>
+        <v>0.01691355066019342</v>
       </c>
       <c r="X63" t="n">
-        <v>0.05466374749791804</v>
+        <v>0.05466118101408804</v>
       </c>
     </row>
     <row r="64">
@@ -5531,61 +5531,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4864960531109634</v>
+        <v>0.4864936899293685</v>
       </c>
       <c r="L64" t="n">
-        <v>0.5431377206405523</v>
+        <v>0.5431377446410841</v>
       </c>
       <c r="M64" t="n">
-        <v>3.890560537641748</v>
+        <v>3.890542885099665</v>
       </c>
       <c r="N64" t="n">
-        <v>4.313103690729363</v>
+        <v>4.313103869066804</v>
       </c>
       <c r="O64" t="n">
-        <v>0.006409802905933022</v>
+        <v>0.006409807875844622</v>
       </c>
       <c r="P64" t="n">
-        <v>0.008542272318553168</v>
+        <v>0.008542268307107475</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.005017525313672798</v>
+        <v>0.005017526424220677</v>
       </c>
       <c r="R64" t="n">
-        <v>0.03170839161994961</v>
+        <v>0.03170840763336748</v>
       </c>
       <c r="S64" t="n">
-        <v>0.06402912355924729</v>
+        <v>0.06403124662608728</v>
       </c>
       <c r="T64" t="n">
-        <v>0.00979860765123622</v>
+        <v>0.009798583575772513</v>
       </c>
       <c r="U64" t="n">
-        <v>0.009527026274918247</v>
+        <v>0.009526956336921881</v>
       </c>
       <c r="V64" t="n">
-        <v>0.006339892454742951</v>
+        <v>0.006339891603730093</v>
       </c>
       <c r="W64" t="n">
-        <v>0.04940829577032713</v>
+        <v>0.04940832218001393</v>
       </c>
       <c r="X64" t="n">
-        <v>0.6905743118075748</v>
+        <v>0.690613054844174</v>
       </c>
     </row>
     <row r="65">
@@ -5611,61 +5611,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4897404220545651</v>
+        <v>0.4897403046305538</v>
       </c>
       <c r="L65" t="n">
-        <v>0.5437688343949164</v>
+        <v>0.5437688325747658</v>
       </c>
       <c r="M65" t="n">
-        <v>3.914793425256979</v>
+        <v>3.914792548262575</v>
       </c>
       <c r="N65" t="n">
-        <v>4.317797149007479</v>
+        <v>4.317797135416597</v>
       </c>
       <c r="O65" t="n">
-        <v>0.006732973302092531</v>
+        <v>0.006732969645197162</v>
       </c>
       <c r="P65" t="n">
-        <v>0.009471195497583998</v>
+        <v>0.00947119468616444</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.005373886004675503</v>
+        <v>0.005373885129201671</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01863029648446468</v>
+        <v>0.01863029197308325</v>
       </c>
       <c r="S65" t="n">
-        <v>0.04832792555866362</v>
+        <v>0.04832805437662822</v>
       </c>
       <c r="T65" t="n">
-        <v>0.009653943102194494</v>
+        <v>0.009653798345946155</v>
       </c>
       <c r="U65" t="n">
-        <v>0.01121575235289177</v>
+        <v>0.01121574952704329</v>
       </c>
       <c r="V65" t="n">
-        <v>0.006828214788860036</v>
+        <v>0.006828205682459057</v>
       </c>
       <c r="W65" t="n">
-        <v>0.01699176735761118</v>
+        <v>0.01699172183921239</v>
       </c>
       <c r="X65" t="n">
-        <v>0.2083707588650521</v>
+        <v>0.2083672247364675</v>
       </c>
     </row>
     <row r="66">
@@ -5691,61 +5691,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.5058386519967449</v>
+        <v>0.5058386592092137</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5433171652241606</v>
+        <v>0.5433171615550187</v>
       </c>
       <c r="M66" t="n">
-        <v>4.034978182807103</v>
+        <v>4.034978236632926</v>
       </c>
       <c r="N66" t="n">
-        <v>4.314443444945271</v>
+        <v>4.314443417609897</v>
       </c>
       <c r="O66" t="n">
-        <v>0.006537349057329465</v>
+        <v>0.006537343265707209</v>
       </c>
       <c r="P66" t="n">
-        <v>0.00901915232173504</v>
+        <v>0.009019149932122054</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.004920225407627007</v>
+        <v>0.004920224573545514</v>
       </c>
       <c r="R66" t="n">
-        <v>0.02817096500762749</v>
+        <v>0.02817095795129423</v>
       </c>
       <c r="S66" t="n">
-        <v>0.04236357422980213</v>
+        <v>0.0423635593002978</v>
       </c>
       <c r="T66" t="n">
-        <v>0.009883080327769876</v>
+        <v>0.009883084880371594</v>
       </c>
       <c r="U66" t="n">
-        <v>0.009862638547905393</v>
+        <v>0.009862670072721531</v>
       </c>
       <c r="V66" t="n">
-        <v>0.006264111497290026</v>
+        <v>0.006264111484163518</v>
       </c>
       <c r="W66" t="n">
-        <v>0.03910171080132697</v>
+        <v>0.0391017083326573</v>
       </c>
       <c r="X66" t="n">
-        <v>0.2476458613928328</v>
+        <v>0.2476458614166958</v>
       </c>
     </row>
     <row r="67">
@@ -5771,61 +5771,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.5593926976864663</v>
+        <v>0.5593936874221827</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5511050561331142</v>
+        <v>0.5511050717263895</v>
       </c>
       <c r="M67" t="n">
-        <v>4.434191938319421</v>
+        <v>4.434199308462619</v>
       </c>
       <c r="N67" t="n">
-        <v>4.372467559538225</v>
+        <v>4.372467675800943</v>
       </c>
       <c r="O67" t="n">
-        <v>0.00581048907559559</v>
+        <v>0.005810291665161235</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01807530368453049</v>
+        <v>0.01807502607034804</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.004460936625821811</v>
+        <v>0.00446092301471738</v>
       </c>
       <c r="R67" t="n">
-        <v>0.01478762518205413</v>
+        <v>0.01478757351791895</v>
       </c>
       <c r="S67" t="n">
-        <v>0.121836908641777</v>
+        <v>0.1218368123171623</v>
       </c>
       <c r="T67" t="n">
-        <v>0.00898860223919159</v>
+        <v>0.00898855832922452</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01645913111349739</v>
+        <v>0.0164591700960285</v>
       </c>
       <c r="V67" t="n">
-        <v>0.008394597612451243</v>
+        <v>0.008394599520519496</v>
       </c>
       <c r="W67" t="n">
-        <v>0.01808808190792437</v>
+        <v>0.01808813795121392</v>
       </c>
       <c r="X67" t="n">
-        <v>0.1492392682967129</v>
+        <v>0.1492351417615763</v>
       </c>
     </row>
     <row r="68">
@@ -5851,61 +5851,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.5709449617807177</v>
+        <v>0.5709449616839343</v>
       </c>
       <c r="L68" t="n">
-        <v>0.5512230301070263</v>
+        <v>0.5512230301309105</v>
       </c>
       <c r="M68" t="n">
-        <v>4.520199018951153</v>
+        <v>4.520199018230743</v>
       </c>
       <c r="N68" t="n">
-        <v>4.373343535299314</v>
+        <v>4.373343535477192</v>
       </c>
       <c r="O68" t="n">
-        <v>0.005442900703252347</v>
+        <v>0.00544290062495028</v>
       </c>
       <c r="P68" t="n">
-        <v>0.02012359435458214</v>
+        <v>0.02012359415180147</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.004907942026679332</v>
+        <v>0.004907942003354723</v>
       </c>
       <c r="R68" t="n">
-        <v>0.0192681917262622</v>
+        <v>0.01926819148613224</v>
       </c>
       <c r="S68" t="n">
-        <v>0.03435876691983841</v>
+        <v>0.03435876596002994</v>
       </c>
       <c r="T68" t="n">
-        <v>0.008974829539068394</v>
+        <v>0.008974829369572696</v>
       </c>
       <c r="U68" t="n">
-        <v>0.01889069927315861</v>
+        <v>0.01889069913334553</v>
       </c>
       <c r="V68" t="n">
-        <v>0.007172005725907654</v>
+        <v>0.007172005715154798</v>
       </c>
       <c r="W68" t="n">
-        <v>0.02531322246784989</v>
+        <v>0.02531322200368933</v>
       </c>
       <c r="X68" t="n">
-        <v>0.04759321663915084</v>
+        <v>0.04759321567507071</v>
       </c>
     </row>
     <row r="69">
@@ -5931,61 +5931,61 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.551076722083462</v>
+        <v>0.5510767095590137</v>
       </c>
       <c r="L69" t="n">
-        <v>0.5516680067571167</v>
+        <v>0.5516679981372379</v>
       </c>
       <c r="M69" t="n">
-        <v>4.372256927767693</v>
+        <v>4.372256834474767</v>
       </c>
       <c r="N69" t="n">
-        <v>4.376661270490092</v>
+        <v>4.376661206282744</v>
       </c>
       <c r="O69" t="n">
-        <v>0.004979062779549797</v>
+        <v>0.00497908617218168</v>
       </c>
       <c r="P69" t="n">
-        <v>0.007484609504053699</v>
+        <v>0.007484715932436031</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.004599505273482471</v>
+        <v>0.004599525347775902</v>
       </c>
       <c r="R69" t="n">
-        <v>0.009819114570553034</v>
+        <v>0.009819150633189153</v>
       </c>
       <c r="S69" t="n">
-        <v>0.007681941897512102</v>
+        <v>0.007681956407666147</v>
       </c>
       <c r="T69" t="n">
-        <v>0.006856055049548118</v>
+        <v>0.006855948287143656</v>
       </c>
       <c r="U69" t="n">
-        <v>0.007845756920376607</v>
+        <v>0.007845890351797346</v>
       </c>
       <c r="V69" t="n">
-        <v>0.006544663043652491</v>
+        <v>0.006544675535161374</v>
       </c>
       <c r="W69" t="n">
-        <v>0.01138945525471451</v>
+        <v>0.01138946622238136</v>
       </c>
       <c r="X69" t="n">
-        <v>0.009393184193468053</v>
+        <v>0.009393189123034662</v>
       </c>
     </row>
     <row r="70">
@@ -6011,61 +6011,61 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.5503708566416453</v>
+        <v>0.5503708593126074</v>
       </c>
       <c r="L70" t="n">
-        <v>0.557175866779264</v>
+        <v>0.5571758683644447</v>
       </c>
       <c r="M70" t="n">
-        <v>4.366998961487805</v>
+        <v>4.36699898138397</v>
       </c>
       <c r="N70" t="n">
-        <v>4.417682680857455</v>
+        <v>4.417682692663453</v>
       </c>
       <c r="O70" t="n">
-        <v>0.005197892510978567</v>
+        <v>0.005197894341232977</v>
       </c>
       <c r="P70" t="n">
-        <v>0.009986064107254541</v>
+        <v>0.009986069237390255</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.006403778328533694</v>
+        <v>0.006403779732745967</v>
       </c>
       <c r="R70" t="n">
-        <v>0.009446083806372806</v>
+        <v>0.009446089063799358</v>
       </c>
       <c r="S70" t="n">
-        <v>0.01226053674075214</v>
+        <v>0.01226054344169278</v>
       </c>
       <c r="T70" t="n">
-        <v>0.006627898998414096</v>
+        <v>0.006627900707491545</v>
       </c>
       <c r="U70" t="n">
-        <v>0.01000198339900437</v>
+        <v>0.01000198877797201</v>
       </c>
       <c r="V70" t="n">
-        <v>0.009263447270604658</v>
+        <v>0.009263449258998484</v>
       </c>
       <c r="W70" t="n">
-        <v>0.01102278787193809</v>
+        <v>0.01102279435530214</v>
       </c>
       <c r="X70" t="n">
-        <v>0.01592689177776248</v>
+        <v>0.01592689196276542</v>
       </c>
     </row>
     <row r="71">
@@ -6091,61 +6091,61 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.5607074877638749</v>
+        <v>0.5607074822876876</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5617671475016892</v>
+        <v>0.5617671464845981</v>
       </c>
       <c r="M71" t="n">
-        <v>4.443982390835941</v>
+        <v>4.443982350059031</v>
       </c>
       <c r="N71" t="n">
-        <v>4.451872624018856</v>
+        <v>4.451872616445272</v>
       </c>
       <c r="O71" t="n">
-        <v>0.006950473483051212</v>
+        <v>0.006950471423871969</v>
       </c>
       <c r="P71" t="n">
-        <v>0.01119878109523018</v>
+        <v>0.01119877911891502</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.006014668364750553</v>
+        <v>0.006014668049505507</v>
       </c>
       <c r="R71" t="n">
-        <v>0.008284751941510156</v>
+        <v>0.008284749194965253</v>
       </c>
       <c r="S71" t="n">
-        <v>0.009500345120199927</v>
+        <v>0.009500343877882789</v>
       </c>
       <c r="T71" t="n">
-        <v>0.009389758893233997</v>
+        <v>0.009389740702690344</v>
       </c>
       <c r="U71" t="n">
-        <v>0.01046663657546794</v>
+        <v>0.01046666255355064</v>
       </c>
       <c r="V71" t="n">
-        <v>0.008066281865285976</v>
+        <v>0.008066274539538424</v>
       </c>
       <c r="W71" t="n">
-        <v>0.01017332114449398</v>
+        <v>0.01017329375482938</v>
       </c>
       <c r="X71" t="n">
-        <v>0.009349611081906201</v>
+        <v>0.009349605301961869</v>
       </c>
     </row>
     <row r="72">
@@ -6171,61 +6171,61 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.567038931825131</v>
+        <v>0.5670389503687139</v>
       </c>
       <c r="L72" t="n">
-        <v>0.5683081016326121</v>
+        <v>0.568308107933293</v>
       </c>
       <c r="M72" t="n">
-        <v>4.491122394156444</v>
+        <v>4.491122532204955</v>
       </c>
       <c r="N72" t="n">
-        <v>4.500570525332932</v>
+        <v>4.500570572237707</v>
       </c>
       <c r="O72" t="n">
-        <v>0.005893813281205717</v>
+        <v>0.00589379611807032</v>
       </c>
       <c r="P72" t="n">
-        <v>0.008319362897141811</v>
+        <v>0.008319355679527348</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.006779453190984728</v>
+        <v>0.006779445853742561</v>
       </c>
       <c r="R72" t="n">
-        <v>0.006317772363817009</v>
+        <v>0.006317765612938105</v>
       </c>
       <c r="S72" t="n">
-        <v>0.008947873969537855</v>
+        <v>0.008947868684717733</v>
       </c>
       <c r="T72" t="n">
-        <v>0.0074814025922358</v>
+        <v>0.007481440482855677</v>
       </c>
       <c r="U72" t="n">
-        <v>0.008082910913349787</v>
+        <v>0.008082809067425175</v>
       </c>
       <c r="V72" t="n">
-        <v>0.00943676046633893</v>
+        <v>0.009436764356661461</v>
       </c>
       <c r="W72" t="n">
-        <v>0.008406874904122995</v>
+        <v>0.008406890567769857</v>
       </c>
       <c r="X72" t="n">
-        <v>0.009851983064998706</v>
+        <v>0.009851982835002476</v>
       </c>
     </row>
     <row r="73">
@@ -6251,61 +6251,61 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.559424568274783</v>
+        <v>0.5594245676823701</v>
       </c>
       <c r="L73" t="n">
-        <v>0.5542417193463152</v>
+        <v>0.5542417201205511</v>
       </c>
       <c r="M73" t="n">
-        <v>4.434429264975574</v>
+        <v>4.434429260564131</v>
       </c>
       <c r="N73" t="n">
-        <v>4.395830335791359</v>
+        <v>4.395830341558166</v>
       </c>
       <c r="O73" t="n">
-        <v>0.00311164960806352</v>
+        <v>0.003111649121862824</v>
       </c>
       <c r="P73" t="n">
-        <v>0.0116854624049021</v>
+        <v>0.01168546120212187</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.002575277009598118</v>
+        <v>0.00257527662245348</v>
       </c>
       <c r="R73" t="n">
-        <v>0.01010762672883607</v>
+        <v>0.0101076249259792</v>
       </c>
       <c r="S73" t="n">
-        <v>0.004155249542480538</v>
+        <v>0.004155248618191218</v>
       </c>
       <c r="T73" t="n">
-        <v>0.004794601447791889</v>
+        <v>0.004794601025422712</v>
       </c>
       <c r="U73" t="n">
-        <v>0.01195657111100483</v>
+        <v>0.01195657076789126</v>
       </c>
       <c r="V73" t="n">
-        <v>0.004188048415705539</v>
+        <v>0.004188048065197536</v>
       </c>
       <c r="W73" t="n">
-        <v>0.01157681147000183</v>
+        <v>0.0115768100500902</v>
       </c>
       <c r="X73" t="n">
-        <v>0.005866718176577782</v>
+        <v>0.005866717650988403</v>
       </c>
     </row>
     <row r="74">
@@ -6331,61 +6331,61 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.5539023547937509</v>
+        <v>0.5539023629027617</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5600764622830117</v>
+        <v>0.5600764649648039</v>
       </c>
       <c r="M74" t="n">
-        <v>4.393303571076886</v>
+        <v>4.393303631473435</v>
       </c>
       <c r="N74" t="n">
-        <v>4.43928257506013</v>
+        <v>4.439282595031615</v>
       </c>
       <c r="O74" t="n">
-        <v>0.003539482780282642</v>
+        <v>0.003539483499011432</v>
       </c>
       <c r="P74" t="n">
-        <v>0.009459343706065427</v>
+        <v>0.009459345923260034</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.003942885578687273</v>
+        <v>0.003942886176049457</v>
       </c>
       <c r="R74" t="n">
-        <v>0.005261280708511905</v>
+        <v>0.005261282194877154</v>
       </c>
       <c r="S74" t="n">
-        <v>0.007590529915465584</v>
+        <v>0.007590530101032967</v>
       </c>
       <c r="T74" t="n">
-        <v>0.005069254833954136</v>
+        <v>0.005069254369872996</v>
       </c>
       <c r="U74" t="n">
-        <v>0.00920143641091797</v>
+        <v>0.009201438612727274</v>
       </c>
       <c r="V74" t="n">
-        <v>0.005810982961156324</v>
+        <v>0.005810982219017776</v>
       </c>
       <c r="W74" t="n">
-        <v>0.00688154944642528</v>
+        <v>0.006881548770074577</v>
       </c>
       <c r="X74" t="n">
-        <v>0.009132958662459483</v>
+        <v>0.009132945815235865</v>
       </c>
     </row>
     <row r="75">
@@ -6411,61 +6411,61 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5371232694513625</v>
+        <v>0.5371232677635055</v>
       </c>
       <c r="L75" t="n">
-        <v>0.5502940645259519</v>
+        <v>0.5502940657481453</v>
       </c>
       <c r="M75" t="n">
-        <v>4.268291721388134</v>
+        <v>4.268291708808715</v>
       </c>
       <c r="N75" t="n">
-        <v>4.366423447898454</v>
+        <v>4.366423457001999</v>
       </c>
       <c r="O75" t="n">
-        <v>0.00439309765914696</v>
+        <v>0.004393098330925994</v>
       </c>
       <c r="P75" t="n">
-        <v>0.01026514405593301</v>
+        <v>0.01026514613395234</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.004907746701731233</v>
+        <v>0.004907747620813534</v>
       </c>
       <c r="R75" t="n">
-        <v>0.009513237997438131</v>
+        <v>0.009513240072563793</v>
       </c>
       <c r="S75" t="n">
-        <v>0.01069227173459293</v>
+        <v>0.0106922747083258</v>
       </c>
       <c r="T75" t="n">
-        <v>0.005999087667311785</v>
+        <v>0.005999088194199288</v>
       </c>
       <c r="U75" t="n">
-        <v>0.01037288258797529</v>
+        <v>0.01037287955940899</v>
       </c>
       <c r="V75" t="n">
-        <v>0.006861234173145976</v>
+        <v>0.006861236984615546</v>
       </c>
       <c r="W75" t="n">
-        <v>0.01130364763349416</v>
+        <v>0.01130365262903175</v>
       </c>
       <c r="X75" t="n">
-        <v>0.01507697132009915</v>
+        <v>0.01507702801412776</v>
       </c>
     </row>
     <row r="76">
@@ -6491,61 +6491,61 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5601812859072123</v>
+        <v>0.5601812787559608</v>
       </c>
       <c r="L76" t="n">
-        <v>0.554208922550998</v>
+        <v>0.5542089220962151</v>
       </c>
       <c r="M76" t="n">
-        <v>4.440064137367118</v>
+        <v>4.440064084116293</v>
       </c>
       <c r="N76" t="n">
-        <v>4.39558591036598</v>
+        <v>4.395585906980745</v>
       </c>
       <c r="O76" t="n">
-        <v>0.003775493534065693</v>
+        <v>0.003775491512225549</v>
       </c>
       <c r="P76" t="n">
-        <v>0.009551691957246717</v>
+        <v>0.009551687739229993</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.002448141847791689</v>
+        <v>0.00244814016872461</v>
       </c>
       <c r="R76" t="n">
-        <v>0.01136745646811261</v>
+        <v>0.01136744886410116</v>
       </c>
       <c r="S76" t="n">
-        <v>0.003804933184227149</v>
+        <v>0.00380493163112478</v>
       </c>
       <c r="T76" t="n">
-        <v>0.005399904901767168</v>
+        <v>0.005399894124058053</v>
       </c>
       <c r="U76" t="n">
-        <v>0.009808984786227829</v>
+        <v>0.009809117191406517</v>
       </c>
       <c r="V76" t="n">
-        <v>0.004113714522596003</v>
+        <v>0.004113705541871169</v>
       </c>
       <c r="W76" t="n">
-        <v>0.01280785370443106</v>
+        <v>0.01280777833539418</v>
       </c>
       <c r="X76" t="n">
-        <v>0.00462627514318698</v>
+        <v>0.004626278689347856</v>
       </c>
     </row>
     <row r="77">
@@ -6571,61 +6571,61 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.5411801492891922</v>
+        <v>0.5411804105489888</v>
       </c>
       <c r="L77" t="n">
-        <v>0.5509854952050122</v>
+        <v>0.5509858024885476</v>
       </c>
       <c r="M77" t="n">
-        <v>4.29852478003157</v>
+        <v>4.298526726860364</v>
       </c>
       <c r="N77" t="n">
-        <v>4.371573398310439</v>
+        <v>4.371575687211229</v>
       </c>
       <c r="O77" t="n">
-        <v>0.003519881062076646</v>
+        <v>0.003519933867878472</v>
       </c>
       <c r="P77" t="n">
-        <v>0.006485058039616344</v>
+        <v>0.006485155834633539</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.002385206538040997</v>
+        <v>0.002385243009228892</v>
       </c>
       <c r="R77" t="n">
-        <v>0.002100626964005671</v>
+        <v>0.002100674969566677</v>
       </c>
       <c r="S77" t="n">
-        <v>0.004512276245548424</v>
+        <v>0.004512340010458235</v>
       </c>
       <c r="T77" t="n">
-        <v>0.004556857174310283</v>
+        <v>0.004557284092022076</v>
       </c>
       <c r="U77" t="n">
-        <v>0.007041647855384667</v>
+        <v>0.007041244241104163</v>
       </c>
       <c r="V77" t="n">
-        <v>0.003440116351912342</v>
+        <v>0.003440205821565175</v>
       </c>
       <c r="W77" t="n">
-        <v>0.003959469132108478</v>
+        <v>0.003959594751331889</v>
       </c>
       <c r="X77" t="n">
-        <v>0.004977059239625063</v>
+        <v>0.00497716523833087</v>
       </c>
     </row>
     <row r="78">
@@ -6651,61 +6651,61 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.5620493770299488</v>
+        <v>0.5620497789278945</v>
       </c>
       <c r="L78" t="n">
-        <v>0.5617157920899372</v>
+        <v>0.5617161432899642</v>
       </c>
       <c r="M78" t="n">
-        <v>4.453974155675245</v>
+        <v>4.453977148152306</v>
       </c>
       <c r="N78" t="n">
-        <v>4.451490274083641</v>
+        <v>4.451492889101668</v>
       </c>
       <c r="O78" t="n">
-        <v>0.002039714068484936</v>
+        <v>0.002039778511000159</v>
       </c>
       <c r="P78" t="n">
-        <v>0.007804765918567542</v>
+        <v>0.007804958772668744</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.00173959441922467</v>
+        <v>0.001739633962485651</v>
       </c>
       <c r="R78" t="n">
-        <v>0.001253633389087856</v>
+        <v>0.00125369219903431</v>
       </c>
       <c r="S78" t="n">
-        <v>0.002290881395380324</v>
+        <v>0.002290996657808809</v>
       </c>
       <c r="T78" t="n">
-        <v>0.003539963244952782</v>
+        <v>0.003540041758084493</v>
       </c>
       <c r="U78" t="n">
-        <v>0.01178935985864458</v>
+        <v>0.01178927481327727</v>
       </c>
       <c r="V78" t="n">
-        <v>0.00284071991216391</v>
+        <v>0.00284076759482531</v>
       </c>
       <c r="W78" t="n">
-        <v>0.003245331114770679</v>
+        <v>0.003245379935922866</v>
       </c>
       <c r="X78" t="n">
-        <v>0.005366437242216487</v>
+        <v>0.005366504594114847</v>
       </c>
     </row>
     <row r="79">
@@ -6725,67 +6725,67 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.5610550899029443</v>
+        <v>0.5610551126721089</v>
       </c>
       <c r="L79" t="n">
-        <v>0.5629314367691181</v>
+        <v>0.5629307178031868</v>
       </c>
       <c r="M79" t="n">
-        <v>4.446570697558703</v>
+        <v>4.446570867100848</v>
       </c>
       <c r="N79" t="n">
-        <v>4.460541586380009</v>
+        <v>4.46053623321937</v>
       </c>
       <c r="O79" t="n">
-        <v>0.002363085701296157</v>
+        <v>0.00236308343499959</v>
       </c>
       <c r="P79" t="n">
-        <v>0.002493468230435302</v>
+        <v>0.002493468373352354</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.001893448215024157</v>
+        <v>0.001893447483266265</v>
       </c>
       <c r="R79" t="n">
-        <v>0.003174909657180953</v>
+        <v>0.003174909123613709</v>
       </c>
       <c r="S79" t="n">
-        <v>0.001052083578125455</v>
+        <v>0.001052246697884329</v>
       </c>
       <c r="T79" t="n">
-        <v>0.003513707948563072</v>
+        <v>0.003513707945610168</v>
       </c>
       <c r="U79" t="n">
-        <v>0.001972333434337066</v>
+        <v>0.001972332749004523</v>
       </c>
       <c r="V79" t="n">
-        <v>0.002786667368745591</v>
+        <v>0.002786666825571839</v>
       </c>
       <c r="W79" t="n">
-        <v>0.003641212570746621</v>
+        <v>0.003641212240208892</v>
       </c>
       <c r="X79" t="n">
-        <v>0.07481062806337774</v>
+        <v>0.07481857707704458</v>
       </c>
     </row>
     <row r="80">
@@ -6805,67 +6805,67 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5736197870707861</v>
+        <v>0.5736197714908451</v>
       </c>
       <c r="L80" t="n">
-        <v>0.5622867659519554</v>
+        <v>0.5622868495240446</v>
       </c>
       <c r="M80" t="n">
-        <v>4.540108243019789</v>
+        <v>4.540108127060703</v>
       </c>
       <c r="N80" t="n">
-        <v>4.455740280144913</v>
+        <v>4.455740902095111</v>
       </c>
       <c r="O80" t="n">
-        <v>0.002604559374820564</v>
+        <v>0.002604561787624004</v>
       </c>
       <c r="P80" t="n">
-        <v>0.003273930704236005</v>
+        <v>0.003273931037001333</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.002206579747553944</v>
+        <v>0.002206582106617566</v>
       </c>
       <c r="R80" t="n">
-        <v>0.003852533191270115</v>
+        <v>0.003852534735711702</v>
       </c>
       <c r="S80" t="n">
-        <v>0.005747786995938819</v>
+        <v>0.005746701697010464</v>
       </c>
       <c r="T80" t="n">
-        <v>0.00383740677726909</v>
+        <v>0.003837364659969451</v>
       </c>
       <c r="U80" t="n">
-        <v>0.002213927207549584</v>
+        <v>0.002213942885896685</v>
       </c>
       <c r="V80" t="n">
-        <v>0.003498847586667879</v>
+        <v>0.00349883241862681</v>
       </c>
       <c r="W80" t="n">
-        <v>0.004670181623124777</v>
+        <v>0.004670192277671668</v>
       </c>
       <c r="X80" t="n">
-        <v>0.5432689495572056</v>
+        <v>0.5430896418189568</v>
       </c>
     </row>
     <row r="81">
@@ -6885,67 +6885,67 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.58328369577433</v>
+        <v>0.583284052080514</v>
       </c>
       <c r="L81" t="n">
-        <v>0.5690284869589906</v>
+        <v>0.5690441876915151</v>
       </c>
       <c r="M81" t="n">
-        <v>4.612023486339785</v>
+        <v>4.612026137412144</v>
       </c>
       <c r="N81" t="n">
-        <v>4.505933052720941</v>
+        <v>4.506049949839943</v>
       </c>
       <c r="O81" t="n">
-        <v>0.002582628585728274</v>
+        <v>0.002582408328243037</v>
       </c>
       <c r="P81" t="n">
-        <v>0.002987382723508012</v>
+        <v>0.002987281711990647</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.001511811570083897</v>
+        <v>0.001511732487889838</v>
       </c>
       <c r="R81" t="n">
-        <v>0.002974690241797417</v>
+        <v>0.002974492494552114</v>
       </c>
       <c r="S81" t="n">
-        <v>0.1909133567417657</v>
+        <v>0.499999999730593</v>
       </c>
       <c r="T81" t="n">
-        <v>0.003968978825643754</v>
+        <v>0.004015465461725584</v>
       </c>
       <c r="U81" t="n">
-        <v>0.003192367213423517</v>
+        <v>0.003150717175609373</v>
       </c>
       <c r="V81" t="n">
-        <v>0.002199579070795655</v>
+        <v>0.002202655323381942</v>
       </c>
       <c r="W81" t="n">
-        <v>0.004117009377314454</v>
+        <v>0.004124613513315251</v>
       </c>
       <c r="X81" t="n">
-        <v>642.9041720277211</v>
+        <v>4565.180873699836</v>
       </c>
     </row>
     <row r="82">
@@ -6965,67 +6965,67 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5822582513598028</v>
+        <v>0.5822581982822064</v>
       </c>
       <c r="L82" t="n">
-        <v>0.5830815191919675</v>
+        <v>0.583081524312934</v>
       </c>
       <c r="M82" t="n">
-        <v>4.604393606839465</v>
+        <v>4.604393211905809</v>
       </c>
       <c r="N82" t="n">
-        <v>4.610519188901112</v>
+        <v>4.61051922700275</v>
       </c>
       <c r="O82" t="n">
-        <v>0.003408430735160765</v>
+        <v>0.003408439951291074</v>
       </c>
       <c r="P82" t="n">
-        <v>0.003027771055686472</v>
+        <v>0.003027768333358216</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.001571448894985017</v>
+        <v>0.001571451330965775</v>
       </c>
       <c r="R82" t="n">
-        <v>0.003598137255798421</v>
+        <v>0.003598140799729524</v>
       </c>
       <c r="S82" t="n">
-        <v>1.000000000101151e-05</v>
+        <v>1.000000000127923e-05</v>
       </c>
       <c r="T82" t="n">
-        <v>0.005852064019649847</v>
+        <v>0.005852099413003272</v>
       </c>
       <c r="U82" t="n">
-        <v>0.003985144854973148</v>
+        <v>0.003985174471848805</v>
       </c>
       <c r="V82" t="n">
-        <v>0.002361311042653331</v>
+        <v>0.002361314219272165</v>
       </c>
       <c r="W82" t="n">
-        <v>0.005058834454341206</v>
+        <v>0.005058841060980574</v>
       </c>
       <c r="X82" t="n">
-        <v>0.02993248382127676</v>
+        <v>0.02993248846064682</v>
       </c>
     </row>
     <row r="83">
@@ -7045,65 +7045,65 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5876714572894921</v>
+        <v>0.5876711610174999</v>
       </c>
       <c r="L83" t="n">
-        <v>0.5691357601150773</v>
+        <v>0.5691351667922803</v>
       </c>
       <c r="M83" t="n">
-        <v>4.644667992207475</v>
+        <v>4.64466578813065</v>
       </c>
       <c r="N83" t="n">
-        <v>4.506724359593225</v>
+        <v>4.506719943619666</v>
       </c>
       <c r="O83" t="n">
-        <v>0.002241059903720495</v>
+        <v>0.002241055256435572</v>
       </c>
       <c r="P83" t="n">
-        <v>0.002265127804840672</v>
+        <v>0.002265128260415887</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.001309787208041391</v>
+        <v>0.001309785911741225</v>
       </c>
       <c r="R83" t="n">
-        <v>0.003202333534829254</v>
+        <v>0.003202334988375708</v>
       </c>
       <c r="S83" t="n">
-        <v>0.003243163409947809</v>
+        <v>0.003243931658189919</v>
       </c>
       <c r="T83" t="n">
-        <v>0.003302577169626289</v>
+        <v>0.003302589639014422</v>
       </c>
       <c r="U83" t="n">
-        <v>0.002727144568369393</v>
+        <v>0.002727140100959592</v>
       </c>
       <c r="V83" t="n">
-        <v>0.002049185019884931</v>
+        <v>0.002049185594031919</v>
       </c>
       <c r="W83" t="n">
-        <v>0.00458307711177768</v>
+        <v>0.00458309623758906</v>
       </c>
       <c r="X83" t="n">
-        <v>0.2375503379844335</v>
+        <v>0.2376346727618726</v>
       </c>
     </row>
     <row r="84">
@@ -7123,65 +7123,65 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5796778824583331</v>
+        <v>0.5796762487829182</v>
       </c>
       <c r="L84" t="n">
-        <v>0.5632793630495724</v>
+        <v>0.5632794283001413</v>
       </c>
       <c r="M84" t="n">
-        <v>4.58519307493649</v>
+        <v>4.585180918231568</v>
       </c>
       <c r="N84" t="n">
-        <v>4.463129874480701</v>
+        <v>4.463130361218673</v>
       </c>
       <c r="O84" t="n">
-        <v>0.002530155692801629</v>
+        <v>0.002530154244760481</v>
       </c>
       <c r="P84" t="n">
-        <v>0.002295237189522304</v>
+        <v>0.002295236842444856</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.001827567959050752</v>
+        <v>0.001827568410149274</v>
       </c>
       <c r="R84" t="n">
-        <v>0.004323044177058612</v>
+        <v>0.004323044007858886</v>
       </c>
       <c r="S84" t="n">
-        <v>0.01399531616859856</v>
+        <v>0.01400123734664974</v>
       </c>
       <c r="T84" t="n">
-        <v>0.003892397722879119</v>
+        <v>0.003890795559112969</v>
       </c>
       <c r="U84" t="n">
-        <v>0.002480768582580709</v>
+        <v>0.002481732524360163</v>
       </c>
       <c r="V84" t="n">
-        <v>0.002816098169427631</v>
+        <v>0.002815873209217402</v>
       </c>
       <c r="W84" t="n">
-        <v>0.005953248108277071</v>
+        <v>0.005952780039535683</v>
       </c>
       <c r="X84" t="n">
-        <v>3.052521528262514</v>
+        <v>3.05430732496039</v>
       </c>
     </row>
     <row r="85">
@@ -7201,65 +7201,67 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5746033622443787</v>
+        <v>0.5615034371120724</v>
       </c>
       <c r="L85" t="n">
-        <v>0.5683371129051785</v>
+        <v>0.5578486878731249</v>
       </c>
       <c r="M85" t="n">
-        <v>4.54742871756644</v>
+        <v>4.449909121929075</v>
       </c>
       <c r="N85" t="n">
-        <v>4.50078428777404</v>
+        <v>4.422693890789051</v>
       </c>
       <c r="O85" t="n">
-        <v>0.002459883314951173</v>
+        <v>0.002404664776428849</v>
       </c>
       <c r="P85" t="n">
-        <v>0.002004905732061631</v>
+        <v>0.002490934635237441</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.001322720936465616</v>
+        <v>0.001499423152704059</v>
       </c>
       <c r="R85" t="n">
-        <v>0.003627316070261307</v>
+        <v>0.00322442643117274</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0008934746959284251</v>
+        <v>0.004846505770106225</v>
       </c>
       <c r="T85" t="n">
-        <v>0.00386395598155971</v>
+        <v>0.003881435980480641</v>
       </c>
       <c r="U85" t="n">
-        <v>0.002894518310069578</v>
+        <v>0.002727291331105313</v>
       </c>
       <c r="V85" t="n">
-        <v>0.001971948090346998</v>
+        <v>0.00219509665626606</v>
       </c>
       <c r="W85" t="n">
-        <v>0.004662059600213462</v>
+        <v>0.003791473736113033</v>
       </c>
       <c r="X85" t="n">
-        <v>0.06596491690938795</v>
+        <v>0.4687610107800105</v>
       </c>
     </row>
     <row r="86">
@@ -7279,65 +7281,67 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5894067212606844</v>
+        <v>0.5764761960078989</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5675744319941294</v>
+        <v>0.5625252989065058</v>
       </c>
       <c r="M86" t="n">
-        <v>4.65757690113081</v>
+        <v>4.561367017387481</v>
       </c>
       <c r="N86" t="n">
-        <v>4.495095910962528</v>
+        <v>4.45751524036424</v>
       </c>
       <c r="O86" t="n">
-        <v>0.002602356806321668</v>
+        <v>0.002567256351642685</v>
       </c>
       <c r="P86" t="n">
-        <v>0.002514288183651582</v>
+        <v>0.003111167934026361</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.001818849690159877</v>
+        <v>0.001963683341232856</v>
       </c>
       <c r="R86" t="n">
-        <v>0.004753060340754134</v>
+        <v>0.003979940085282489</v>
       </c>
       <c r="S86" t="n">
-        <v>0.001558673344689067</v>
+        <v>0.00556696843896125</v>
       </c>
       <c r="T86" t="n">
-        <v>0.003900122401520284</v>
+        <v>0.00391321393910759</v>
       </c>
       <c r="U86" t="n">
-        <v>0.003534835463378525</v>
+        <v>0.003210543545450449</v>
       </c>
       <c r="V86" t="n">
-        <v>0.002822616055199468</v>
+        <v>0.003091242939442275</v>
       </c>
       <c r="W86" t="n">
-        <v>0.006873249310763641</v>
+        <v>0.005106789753904796</v>
       </c>
       <c r="X86" t="n">
-        <v>0.08605287698308521</v>
+        <v>0.5271548419125707</v>
       </c>
     </row>
     <row r="87">
@@ -7357,65 +7361,67 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.5852585427094423</v>
+        <v>0.582386435138936</v>
       </c>
       <c r="L87" t="n">
-        <v>0.5860747888759458</v>
+        <v>0.5828609868742576</v>
       </c>
       <c r="M87" t="n">
-        <v>4.675916314716923</v>
+        <v>4.605347379894655</v>
       </c>
       <c r="N87" t="n">
-        <v>4.634880754952861</v>
+        <v>4.608878318764571</v>
       </c>
       <c r="O87" t="n">
-        <v>0.003847450500224445</v>
+        <v>0.003732067368151137</v>
       </c>
       <c r="P87" t="n">
-        <v>0.002121395293652149</v>
+        <v>0.003477380180688177</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.001641241416160619</v>
+        <v>0.001795807407723915</v>
       </c>
       <c r="R87" t="n">
-        <v>0.004282588133021035</v>
+        <v>0.003999108821948573</v>
       </c>
       <c r="S87" t="n">
-        <v>1.000000000293862e-05</v>
+        <v>1.000000001821043e-05</v>
       </c>
       <c r="T87" t="n">
-        <v>0.006889885892129998</v>
+        <v>0.006580185287698198</v>
       </c>
       <c r="U87" t="n">
-        <v>0.003749616520646193</v>
+        <v>0.004240037938703946</v>
       </c>
       <c r="V87" t="n">
-        <v>0.002526215367460178</v>
+        <v>0.002729361684105172</v>
       </c>
       <c r="W87" t="n">
-        <v>0.006225362833718035</v>
+        <v>0.005738988688895199</v>
       </c>
       <c r="X87" t="n">
-        <v>0.0282144013148741</v>
+        <v>0.02789670243413716</v>
       </c>
     </row>
     <row r="88">
@@ -7435,65 +7441,67 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.590586229268512</v>
+        <v>0.5835775281999703</v>
       </c>
       <c r="L88" t="n">
-        <v>0.571148589813092</v>
+        <v>0.5691531595995394</v>
       </c>
       <c r="M88" t="n">
-        <v>4.666351041259506</v>
+        <v>4.614209716329934</v>
       </c>
       <c r="N88" t="n">
-        <v>4.521714113781278</v>
+        <v>4.506861091638576</v>
       </c>
       <c r="O88" t="n">
-        <v>0.00250076556649482</v>
+        <v>0.002802076666954088</v>
       </c>
       <c r="P88" t="n">
-        <v>0.01010940010205734</v>
+        <v>0.003221000005726236</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.001303833929158798</v>
+        <v>0.001630591827665489</v>
       </c>
       <c r="R88" t="n">
-        <v>0.002753100256459732</v>
+        <v>0.003226441766988511</v>
       </c>
       <c r="S88" t="n">
-        <v>0.329764195321686</v>
+        <v>0.144117561243758</v>
       </c>
       <c r="T88" t="n">
-        <v>0.003952943094007184</v>
+        <v>0.004308761292143156</v>
       </c>
       <c r="U88" t="n">
-        <v>0.0196176430429537</v>
+        <v>0.003608187168975015</v>
       </c>
       <c r="V88" t="n">
-        <v>0.001930786774262084</v>
+        <v>0.002337473928321929</v>
       </c>
       <c r="W88" t="n">
-        <v>0.003850712643097961</v>
+        <v>0.004471415027046777</v>
       </c>
       <c r="X88" t="n">
-        <v>1335.927568934657</v>
+        <v>305.0250489685977</v>
       </c>
     </row>
     <row r="89">
@@ -7513,65 +7521,65 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.5779806317272085</v>
+        <v>0.5779818598694213</v>
       </c>
       <c r="L89" t="n">
-        <v>0.5695979852002089</v>
+        <v>0.5696125797768093</v>
       </c>
       <c r="M89" t="n">
-        <v>4.572562927515825</v>
+        <v>4.572572067036488</v>
       </c>
       <c r="N89" t="n">
-        <v>4.510171875638907</v>
+        <v>4.510280497849108</v>
       </c>
       <c r="O89" t="n">
-        <v>0.003093786028281051</v>
+        <v>0.003093548311842311</v>
       </c>
       <c r="P89" t="n">
-        <v>0.003321637970836656</v>
+        <v>0.003321561137588121</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.001758510285614008</v>
+        <v>0.001758460613857978</v>
       </c>
       <c r="R89" t="n">
-        <v>0.002971785580675948</v>
+        <v>0.002971652462173765</v>
       </c>
       <c r="S89" t="n">
-        <v>0.2053916529553006</v>
+        <v>0.3880154226269689</v>
       </c>
       <c r="T89" t="n">
-        <v>0.005051577085139772</v>
+        <v>0.005055565530781064</v>
       </c>
       <c r="U89" t="n">
-        <v>0.00345970529649027</v>
+        <v>0.003466860522053785</v>
       </c>
       <c r="V89" t="n">
-        <v>0.002430221685954793</v>
+        <v>0.002430611735171493</v>
       </c>
       <c r="W89" t="n">
-        <v>0.003995961550184108</v>
+        <v>0.003998396948089012</v>
       </c>
       <c r="X89" t="n">
-        <v>698.8853185529664</v>
+        <v>2520.098227292238</v>
       </c>
     </row>
     <row r="90">
@@ -7593,63 +7601,65 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5729495712298516</v>
+        <v>0.5785262774142708</v>
       </c>
       <c r="L90" t="n">
-        <v>0.538090711221303</v>
+        <v>0.540660076605912</v>
       </c>
       <c r="M90" t="n">
-        <v>4.535119873192953</v>
+        <v>4.576623446244543</v>
       </c>
       <c r="N90" t="n">
-        <v>4.275474091185615</v>
+        <v>4.294621419601994</v>
       </c>
       <c r="O90" t="n">
-        <v>0.004502802329264286</v>
+        <v>0.003790880805482992</v>
       </c>
       <c r="P90" t="n">
-        <v>0.003779778810490576</v>
+        <v>0.004555483370454207</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.0085059119133857</v>
+        <v>0.007218335752760919</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01338573068380969</v>
+        <v>0.01223480968492479</v>
       </c>
       <c r="S90" t="n">
-        <v>0.002597984173850604</v>
+        <v>0.002114526736421032</v>
       </c>
       <c r="T90" t="n">
-        <v>0.009392359537057388</v>
+        <v>0.006409198983616883</v>
       </c>
       <c r="U90" t="n">
-        <v>0.006127481314092945</v>
+        <v>0.00567521827726613</v>
       </c>
       <c r="V90" t="n">
-        <v>0.01297714657944554</v>
+        <v>0.006341614426295619</v>
       </c>
       <c r="W90" t="n">
-        <v>0.03528431992152802</v>
+        <v>0.03083156631538217</v>
       </c>
       <c r="X90" t="n">
-        <v>0.07255680291766919</v>
+        <v>0.05694552213501926</v>
       </c>
     </row>
   </sheetData>
